--- a/output/New York_Dental_Clinics_Enriched.xlsx
+++ b/output/New York_Dental_Clinics_Enriched.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,6 +68,11 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
@@ -189,19 +194,19 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -718,23 +723,23 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="36" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
+    <col width="36" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
     <col width="8" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
   </cols>
@@ -855,7 +860,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="9" t="n">
         <v>1</v>
       </c>
@@ -945,7 +950,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="12" t="n">
         <v>2</v>
       </c>
@@ -1035,7 +1040,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="9" t="n">
         <v>3</v>
       </c>
@@ -1125,7 +1130,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="12" t="n">
         <v>4</v>
       </c>
@@ -1215,23 +1220,23 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="9" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>ORAL Dental Studio NYC</t>
+          <t>Expert Dental - Midtown</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>(646) 663-7633</t>
+          <t>(212) 763-3383</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>131 Essex St Fl 2, New York, NY 10002, USA</t>
+          <t>110 E 40th St #104, New York, NY 10016, USA</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -1241,25 +1246,25 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>https://www.oraldentalstudio.com/</t>
+          <t>https://www.expertdentalnyc.com/</t>
         </is>
       </c>
       <c r="G8" s="9" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>458</v>
+        <v>2156</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 6:00 PM</t>
+          <t>Monday: 9:00 AM – 7:00 PM</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>40.7200496</v>
+        <v>40.7503706</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>-73.98762359999999</v>
+        <v>-73.9780354</v>
       </c>
       <c r="L8" s="10" t="inlineStr">
         <is>
@@ -1288,7 +1293,7 @@
       </c>
       <c r="Q8" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, LinkedIn</t>
+          <t>Facebook, Instagram</t>
         </is>
       </c>
       <c r="R8" s="10" t="inlineStr">
@@ -1305,23 +1310,23 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="12" t="n">
         <v>6</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Expert Dental - Midtown</t>
+          <t>ORAL Dental Studio NYC</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>(212) 763-3383</t>
+          <t>(646) 663-7633</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>110 E 40th St #104, New York, NY 10016, USA</t>
+          <t>131 Essex St Fl 2, New York, NY 10002, USA</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
@@ -1331,25 +1336,25 @@
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>https://www.expertdentalnyc.com/</t>
+          <t>https://www.oraldentalstudio.com/</t>
         </is>
       </c>
       <c r="G9" s="12" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>2156</v>
+        <v>458</v>
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 7:00 PM</t>
+          <t>Monday: 9:00 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J9" s="12" t="n">
-        <v>40.7503706</v>
+        <v>40.7200496</v>
       </c>
       <c r="K9" s="12" t="n">
-        <v>-73.9780354</v>
+        <v>-73.98762359999999</v>
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
@@ -1378,7 +1383,7 @@
       </c>
       <c r="Q9" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram</t>
+          <t>Facebook, Instagram, LinkedIn</t>
         </is>
       </c>
       <c r="R9" s="13" t="inlineStr">
@@ -1395,23 +1400,23 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" s="9" t="n">
         <v>7</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Pearl Dental NYC</t>
+          <t>Midtown Dental Group Fashion District</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>(212) 344-9317</t>
+          <t>(212) 730-4440</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>233 Broadway 18 Suite 1801, New York, NY 10279, USA</t>
+          <t>241 W 37th St Ground Floor, New York, NY 10018, USA</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -1421,44 +1426,44 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>https://www.pearldentalnyc.com/</t>
+          <t>http://www.midtowndentalgroup.com/</t>
         </is>
       </c>
       <c r="G10" s="9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>475</v>
+        <v>734</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>Monday: 8:00 AM – 5:00 PM</t>
+          <t>Monday: 9:00 AM – 5:45 PM</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>40.7123834</v>
+        <v>40.7538706</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>-74.0079386</v>
+        <v>-73.9909457</v>
       </c>
       <c r="L10" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4 dentists</t>
         </is>
       </c>
       <c r="N10" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O10" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="P10" s="10" t="inlineStr">
@@ -1468,12 +1473,12 @@
       </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Facebook, Instagram</t>
         </is>
       </c>
       <c r="R10" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ZocDoc</t>
         </is>
       </c>
       <c r="S10" s="9" t="n">
@@ -1485,23 +1490,23 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="12" t="n">
         <v>8</v>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Midtown Dental Care Associates</t>
+          <t>Pearl Dental NYC</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>(212) 685-4730</t>
+          <t>(212) 344-9317</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>12 E 41st St Ste 1100, New York, NY 10017, USA</t>
+          <t>233 Broadway 18 Suite 1801, New York, NY 10279, USA</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -1511,29 +1516,29 @@
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>https://www.midtowndentalcareassociates.com/?utm_source=gmb&amp;utm_medium=organic</t>
+          <t>https://www.pearldentalnyc.com/</t>
         </is>
       </c>
       <c r="G11" s="12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>573</v>
+        <v>475</v>
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>Monday: 8:00 AM – 7:00 PM</t>
+          <t>Monday: 8:00 AM – 5:00 PM</t>
         </is>
       </c>
       <c r="J11" s="12" t="n">
-        <v>40.752382</v>
+        <v>40.7123834</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>-73.980661</v>
+        <v>-74.0079386</v>
       </c>
       <c r="L11" s="13" t="inlineStr">
         <is>
-          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M11" s="13" t="inlineStr">
@@ -1558,7 +1563,7 @@
       </c>
       <c r="Q11" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R11" s="13" t="inlineStr">
@@ -1575,23 +1580,23 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" s="9" t="n">
         <v>9</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>NYC Dental Center</t>
+          <t>Midtown Dental Care Associates</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>(646) 861-3070</t>
+          <t>(212) 685-4730</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>216 E 39th St #1, New York, NY 10016, USA</t>
+          <t>12 E 41st St Ste 1100, New York, NY 10017, USA</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -1601,29 +1606,29 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>https://weence.com/dentists/new-york-1/nyc-dental-center/</t>
+          <t>https://www.midtowndentalcareassociates.com/?utm_source=gmb&amp;utm_medium=organic</t>
         </is>
       </c>
       <c r="G12" s="9" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>255</v>
+        <v>573</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>Monday: 10:00 AM – 6:00 PM</t>
+          <t>Monday: 8:00 AM – 7:00 PM</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>40.7483698</v>
+        <v>40.752382</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>-73.9752108</v>
+        <v>-73.980661</v>
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
-          <t>Cosmetic, Implants, Periodontics, Oral Surgery</t>
+          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
         </is>
       </c>
       <c r="M12" s="10" t="inlineStr">
@@ -1633,12 +1638,12 @@
       </c>
       <c r="N12" s="10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O12" s="10" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P12" s="10" t="inlineStr">
@@ -1648,7 +1653,7 @@
       </c>
       <c r="Q12" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Facebook, Instagram</t>
         </is>
       </c>
       <c r="R12" s="10" t="inlineStr">
@@ -1665,23 +1670,23 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" s="12" t="n">
         <v>10</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>NYC Smile Spa</t>
+          <t>NYC Dental Center</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>(646) 374-2242</t>
+          <t>(646) 861-3070</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>30 E 60th St Ste 1201, New York, NY 10022, USA</t>
+          <t>216 E 39th St #1, New York, NY 10016, USA</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
@@ -1691,29 +1696,29 @@
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>https://www.nycsmilespa.com/</t>
+          <t>https://weence.com/dentists/new-york-1/nyc-dental-center/</t>
         </is>
       </c>
       <c r="G13" s="12" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>395</v>
+        <v>255</v>
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>Monday: 8:00 AM – 6:00 PM</t>
+          <t>Monday: 10:00 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J13" s="12" t="n">
-        <v>40.7637066</v>
+        <v>40.7483698</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>-73.970242</v>
+        <v>-73.9752108</v>
       </c>
       <c r="L13" s="13" t="inlineStr">
         <is>
-          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
+          <t>Implants, Periodontics, Endodontics, Oral Surgery</t>
         </is>
       </c>
       <c r="M13" s="13" t="inlineStr">
@@ -1728,7 +1733,7 @@
       </c>
       <c r="O13" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="P13" s="13" t="inlineStr">
@@ -1738,7 +1743,7 @@
       </c>
       <c r="Q13" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, YouTube</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R13" s="13" t="inlineStr">
@@ -1755,23 +1760,23 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="9" t="n">
         <v>11</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>212 Dental Care</t>
+          <t>NYC Smile Spa</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>(888) 506-9583</t>
+          <t>(646) 374-2242</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>286 Madison Ave 10th Floor, New York, NY 10017, USA</t>
+          <t>30 E 60th St Ste 1201, New York, NY 10022, USA</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -1781,29 +1786,29 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>http://212dentalcare.com/</t>
+          <t>https://www.nycsmilespa.com/</t>
         </is>
       </c>
       <c r="G14" s="9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>3285</v>
+        <v>395</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>Monday: 8:00 AM – 8:00 PM</t>
+          <t>Monday: 8:00 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>40.751693</v>
+        <v>40.7637066</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>-73.9803106</v>
+        <v>-73.970242</v>
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
@@ -1813,7 +1818,7 @@
       </c>
       <c r="N14" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O14" s="10" t="inlineStr">
@@ -1828,7 +1833,7 @@
       </c>
       <c r="Q14" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Facebook, Instagram, YouTube</t>
         </is>
       </c>
       <c r="R14" s="10" t="inlineStr">
@@ -1845,23 +1850,23 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="12" t="n">
         <v>12</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>SoHo Dental Group NYC</t>
+          <t>212 Dental Care</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>(212) 878-7646</t>
+          <t>(888) 506-9583</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>552 Broadway #505, New York, NY 10012, USA</t>
+          <t>286 Madison Ave 10th Floor, New York, NY 10017, USA</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -1871,25 +1876,25 @@
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>https://www.sohodentalgroup.com/?utm_campaign=gmb&amp;utm_medium=organic&amp;utm_source=gmb</t>
+          <t>http://212dentalcare.com/</t>
         </is>
       </c>
       <c r="G15" s="12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>540</v>
+        <v>3285</v>
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 6:00 PM</t>
+          <t>Monday: 8:00 AM – 8:00 PM</t>
         </is>
       </c>
       <c r="J15" s="12" t="n">
-        <v>40.7237243</v>
+        <v>40.751693</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>-73.99803159999999</v>
+        <v>-73.9803106</v>
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
@@ -1935,23 +1940,23 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="9" t="n">
         <v>13</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Studio Smiles NYC</t>
+          <t>SoHo Dental Group NYC</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>(646) 470-1376</t>
+          <t>(212) 878-7646</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>41 Park Ave # 1C, New York, NY 10016, USA</t>
+          <t>552 Broadway #505, New York, NY 10012, USA</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -1961,29 +1966,29 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>http://www.studiosmilesnyc.com/</t>
+          <t>https://www.sohodentalgroup.com/?utm_campaign=gmb&amp;utm_medium=organic&amp;utm_source=gmb</t>
         </is>
       </c>
       <c r="G16" s="9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>611</v>
+        <v>540</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>Monday: 8:00 AM – 6:00 PM</t>
+          <t>Monday: 9:00 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>40.748366</v>
+        <v>40.7237243</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>-73.97995039999999</v>
+        <v>-73.99803159999999</v>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr">
@@ -1993,12 +1998,12 @@
       </c>
       <c r="N16" s="10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O16" s="10" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P16" s="10" t="inlineStr">
@@ -2008,7 +2013,7 @@
       </c>
       <c r="Q16" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, Twitter/X</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R16" s="10" t="inlineStr">
@@ -2025,23 +2030,23 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="12" t="n">
         <v>14</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Lumia Dental PLLC</t>
+          <t>Studio Smiles NYC</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>(212) 287-1275</t>
+          <t>(646) 470-1376</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>160 Broadway #1004, New York, NY 10038, USA</t>
+          <t>41 Park Ave # 1C, New York, NY 10016, USA</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
@@ -2051,14 +2056,14 @@
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>https://www.lumiadental.com/</t>
+          <t>http://www.studiosmilesnyc.com/</t>
         </is>
       </c>
       <c r="G17" s="12" t="n">
         <v>4.9</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>768</v>
+        <v>611</v>
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
@@ -2066,14 +2071,14 @@
         </is>
       </c>
       <c r="J17" s="12" t="n">
-        <v>40.70937199999999</v>
+        <v>40.748366</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>-74.00997500000001</v>
+        <v>-73.97995039999999</v>
       </c>
       <c r="L17" s="13" t="inlineStr">
         <is>
-          <t>Cosmetic, Orthodontics, Periodontics, Endodontics</t>
+          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
         </is>
       </c>
       <c r="M17" s="13" t="inlineStr">
@@ -2088,22 +2093,22 @@
       </c>
       <c r="O17" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="P17" s="13" t="inlineStr">
         <is>
-          <t>Since 2008</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q17" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, Twitter/X, LinkedIn</t>
+          <t>Facebook, Instagram, Twitter/X</t>
         </is>
       </c>
       <c r="R17" s="13" t="inlineStr">
         <is>
-          <t>ZocDoc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S17" s="12" t="n">
@@ -2115,23 +2120,23 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="9" t="n">
         <v>15</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>My NYC Dentist - Hudson Street Dental</t>
+          <t>Lumia Dental PLLC</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>(212) 359-0064</t>
+          <t>(212) 287-1275</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>90 Vandam St, New York, NY 10013, USA</t>
+          <t>160 Broadway #1004, New York, NY 10038, USA</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -2141,29 +2146,29 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>https://www.mynyc-dentist.com/</t>
+          <t>https://www.lumiadental.com/</t>
         </is>
       </c>
       <c r="G18" s="9" t="n">
         <v>4.9</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>289</v>
+        <v>768</v>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>Monday: 8:30 AM – 6:00 PM</t>
+          <t>Monday: 8:00 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>40.7265687</v>
+        <v>40.70937199999999</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>-74.00812239999999</v>
+        <v>-74.00997500000001</v>
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
+          <t>Cosmetic, Orthodontics, Periodontics, Endodontics</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr">
@@ -2173,22 +2178,22 @@
       </c>
       <c r="N18" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O18" s="10" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P18" s="10" t="inlineStr">
         <is>
-          <t>Since 2009</t>
+          <t>Since 2008</t>
         </is>
       </c>
       <c r="Q18" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram</t>
+          <t>Facebook, Instagram, Twitter/X, LinkedIn</t>
         </is>
       </c>
       <c r="R18" s="10" t="inlineStr">
@@ -2205,23 +2210,23 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="12" t="n">
         <v>16</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Diamond District Dental NYC - Midtown Dentist</t>
+          <t>My NYC Dentist - Hudson Street Dental</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>(212) 759-5595</t>
+          <t>(212) 359-0064</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>10 W 46th St #1401, New York, NY 10036, USA</t>
+          <t>90 Vandam St, New York, NY 10013, USA</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
@@ -2231,25 +2236,25 @@
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>https://www.dddentalnyc.com/?utm_campaign=gmb</t>
+          <t>https://www.mynyc-dentist.com/</t>
         </is>
       </c>
       <c r="G19" s="12" t="n">
         <v>4.9</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>595</v>
+        <v>289</v>
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 6:00 PM</t>
+          <t>Monday: 8:30 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J19" s="12" t="n">
-        <v>40.7563177</v>
+        <v>40.7265687</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>-73.9800044</v>
+        <v>-74.00812239999999</v>
       </c>
       <c r="L19" s="13" t="inlineStr">
         <is>
@@ -2263,7 +2268,7 @@
       </c>
       <c r="N19" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O19" s="13" t="inlineStr">
@@ -2273,17 +2278,17 @@
       </c>
       <c r="P19" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Since 2009</t>
         </is>
       </c>
       <c r="Q19" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, YouTube, TikTok</t>
+          <t>Facebook, Instagram</t>
         </is>
       </c>
       <c r="R19" s="13" t="inlineStr">
         <is>
-          <t>ZocDoc, Laser Dentistry</t>
+          <t>ZocDoc</t>
         </is>
       </c>
       <c r="S19" s="12" t="n">
@@ -2295,23 +2300,23 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="9" t="n">
         <v>17</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Wall Street Dental Spa - Financial District</t>
+          <t>Diamond District Dental NYC - Midtown Dentist</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>(212) 514-5514</t>
+          <t>(212) 759-5595</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>30 Wall St #720, New York, NY 10005, USA</t>
+          <t>10 W 46th St #1401, New York, NY 10036, USA</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -2321,14 +2326,14 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>https://wallstdentalspanyc.com/</t>
+          <t>https://www.dddentalnyc.com/?utm_campaign=gmb</t>
         </is>
       </c>
       <c r="G20" s="9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>1406</v>
+        <v>595</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
@@ -2336,10 +2341,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>40.7069897</v>
+        <v>40.7563177</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>-74.01027259999999</v>
+        <v>-73.9800044</v>
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
@@ -2368,12 +2373,12 @@
       </c>
       <c r="Q20" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, Twitter/X, YouTube</t>
+          <t>Facebook, Instagram, YouTube, TikTok</t>
         </is>
       </c>
       <c r="R20" s="10" t="inlineStr">
         <is>
-          <t>Digital Imaging</t>
+          <t>ZocDoc, Laser Dentistry</t>
         </is>
       </c>
       <c r="S20" s="9" t="n">
@@ -2385,23 +2390,23 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="12" t="n">
         <v>18</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Smile Cafe Dental Spa</t>
+          <t>Wall Street Dental Spa - Financial District</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>(212) 779-7743</t>
+          <t>(212) 514-5514</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Smile Cafe Dental Spa, 45 Park Ave Professional Unit 1, New York, NY 10016, USA</t>
+          <t>30 Wall St #720, New York, NY 10005, USA</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
@@ -2411,25 +2416,25 @@
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>http://www.smilecafeny.com/</t>
+          <t>https://wallstdentalspanyc.com/</t>
         </is>
       </c>
       <c r="G21" s="12" t="n">
         <v>4.8</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>1099</v>
+        <v>1406</v>
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 8:00 PM</t>
+          <t>Monday: 9:00 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J21" s="12" t="n">
-        <v>40.7486592</v>
+        <v>40.7069897</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>-73.9797464</v>
+        <v>-74.01027259999999</v>
       </c>
       <c r="L21" s="13" t="inlineStr">
         <is>
@@ -2443,7 +2448,7 @@
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O21" s="13" t="inlineStr">
@@ -2453,17 +2458,17 @@
       </c>
       <c r="P21" s="13" t="inlineStr">
         <is>
-          <t>Since 2023</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q21" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, YouTube</t>
+          <t>Facebook, Instagram, Twitter/X, YouTube</t>
         </is>
       </c>
       <c r="R21" s="13" t="inlineStr">
         <is>
-          <t>ZocDoc, Digital Imaging, Same-Day Crowns, Laser Dentistry</t>
+          <t>Digital Imaging</t>
         </is>
       </c>
       <c r="S21" s="12" t="n">
@@ -2475,23 +2480,23 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="9" t="n">
         <v>19</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>172 NYC Dental</t>
+          <t>Smile Cafe Dental Spa</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>(646) 921-5541</t>
+          <t>(212) 779-7743</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>172 Madison Ave Comm 1, New York, NY 10016, USA</t>
+          <t>Smile Cafe Dental Spa, 45 Park Ave Professional Unit 1, New York, NY 10016, USA</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -2501,25 +2506,25 @@
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>https://172nycdental.com/?utm_source=google&amp;utm_medium=organic&amp;utm_campaign=gmb</t>
+          <t>http://www.smilecafeny.com/</t>
         </is>
       </c>
       <c r="G22" s="9" t="n">
         <v>4.8</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>260</v>
+        <v>1099</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>Monday: 7:30 AM – 6:30 PM</t>
+          <t>Monday: 9:00 AM – 8:00 PM</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>40.7474307</v>
+        <v>40.7486592</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>-73.9835995</v>
+        <v>-73.9797464</v>
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
@@ -2533,7 +2538,7 @@
       </c>
       <c r="N22" s="10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O22" s="10" t="inlineStr">
@@ -2543,17 +2548,17 @@
       </c>
       <c r="P22" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Since 2023</t>
         </is>
       </c>
       <c r="Q22" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, Twitter/X</t>
+          <t>Facebook, Instagram, YouTube</t>
         </is>
       </c>
       <c r="R22" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ZocDoc, Digital Imaging, Same-Day Crowns, Laser Dentistry</t>
         </is>
       </c>
       <c r="S22" s="9" t="n">
@@ -2565,23 +2570,23 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="12" t="n">
         <v>20</v>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>New York General Dentistry</t>
+          <t>172 NYC Dental</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>(212) 838-0842</t>
+          <t>(646) 921-5541</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>133 E 58th St Ste 409, New York, NY 10022, USA</t>
+          <t>172 Madison Ave Comm 1, New York, NY 10016, USA</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
@@ -2591,29 +2596,29 @@
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>https://newyorkgeneraldentistry.com/?utm_source=GMBlisting&amp;utm_medium=organic</t>
+          <t>https://172nycdental.com/?utm_source=google&amp;utm_medium=organic&amp;utm_campaign=gmb</t>
         </is>
       </c>
       <c r="G23" s="12" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>371</v>
+        <v>260</v>
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>Monday: 8:30 AM – 5:30 PM</t>
+          <t>Monday: 7:30 AM – 6:30 PM</t>
         </is>
       </c>
       <c r="J23" s="12" t="n">
-        <v>40.7619525</v>
+        <v>40.7474307</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>-73.9689326</v>
+        <v>-73.9835995</v>
       </c>
       <c r="L23" s="13" t="inlineStr">
         <is>
-          <t>General Dentistry, Cosmetic, Orthodontics, Endodontics</t>
+          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
         </is>
       </c>
       <c r="M23" s="13" t="inlineStr">
@@ -2623,12 +2628,12 @@
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O23" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="P23" s="13" t="inlineStr">
@@ -2638,12 +2643,12 @@
       </c>
       <c r="Q23" s="13" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook, Instagram, Twitter/X</t>
         </is>
       </c>
       <c r="R23" s="13" t="inlineStr">
         <is>
-          <t>Laser Dentistry</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S23" s="12" t="n">
@@ -2655,23 +2660,23 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="20" customHeight="1">
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="9" t="n">
         <v>21</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>TriBeCa Dental Associates | Murray</t>
+          <t>New York General Dentistry</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>(212) 671-3749</t>
+          <t>(212) 838-0842</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>21 Murray St 4th floor, New York, NY 10007, USA</t>
+          <t>133 E 58th St Ste 409, New York, NY 10022, USA</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -2681,29 +2686,29 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>https://tribeca.dental/</t>
+          <t>https://newyorkgeneraldentistry.com/?utm_source=GMBlisting&amp;utm_medium=organic</t>
         </is>
       </c>
       <c r="G24" s="9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>1502</v>
+        <v>371</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>Monday: 8:00 AM – 4:00 PM</t>
+          <t>Monday: 8:30 AM – 5:30 PM</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>40.7137936</v>
+        <v>40.7619525</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>-74.0081888</v>
+        <v>-73.9689326</v>
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>Cosmetic, Implants, Orthodontics, Periodontics</t>
+          <t>General Dentistry, Cosmetic, Orthodontics, Endodontics</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr">
@@ -2728,12 +2733,12 @@
       </c>
       <c r="Q24" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="R24" s="10" t="inlineStr">
         <is>
-          <t>Digital Imaging, Same-Day Crowns</t>
+          <t>Laser Dentistry</t>
         </is>
       </c>
       <c r="S24" s="9" t="n">
@@ -2745,23 +2750,23 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1">
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="12" t="n">
         <v>22</v>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Midtown Dental Group Fashion District</t>
+          <t>TriBeCa Dental Associates | Murray</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>(212) 730-4440</t>
+          <t>(212) 671-3749</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>241 W 37th St Ground Floor, New York, NY 10018, USA</t>
+          <t>21 Murray St 4th floor, New York, NY 10007, USA</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
@@ -2771,44 +2776,44 @@
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>http://www.midtowndentalgroup.com/</t>
+          <t>https://tribeca.dental/</t>
         </is>
       </c>
       <c r="G25" s="12" t="n">
         <v>4.9</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>734</v>
+        <v>1502</v>
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 5:45 PM</t>
+          <t>Monday: 8:00 AM – 4:00 PM</t>
         </is>
       </c>
       <c r="J25" s="12" t="n">
-        <v>40.7538706</v>
+        <v>40.7137936</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>-73.9909457</v>
+        <v>-74.0081888</v>
       </c>
       <c r="L25" s="13" t="inlineStr">
         <is>
-          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
+          <t>Cosmetic, Implants, Orthodontics, Periodontics</t>
         </is>
       </c>
       <c r="M25" s="13" t="inlineStr">
         <is>
-          <t>4 dentists</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O25" s="13" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P25" s="13" t="inlineStr">
@@ -2823,7 +2828,7 @@
       </c>
       <c r="R25" s="13" t="inlineStr">
         <is>
-          <t>ZocDoc</t>
+          <t>Digital Imaging, Same-Day Crowns</t>
         </is>
       </c>
       <c r="S25" s="12" t="n">
@@ -2835,7 +2840,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1">
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="9" t="n">
         <v>23</v>
       </c>
@@ -2925,23 +2930,23 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="12" t="n">
         <v>24</v>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Midtown Dental Group Upper East Side</t>
+          <t>Sachar Dental NYC</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>(212) 588-1809</t>
+          <t>(212) 752-1163</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>30 E 60th St Ste 2402, New York, NY 10022, USA</t>
+          <t>20 E 46th St Rm 1301, New York, NY 10017, USA</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
@@ -2951,25 +2956,25 @@
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>https://midtowndentalgroup.com/locations/uppereastside/</t>
+          <t>https://www.sachardental.com/</t>
         </is>
       </c>
       <c r="G27" s="12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>505</v>
+        <v>414</v>
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 5:00 PM</t>
+          <t>Monday: 8:00 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J27" s="12" t="n">
-        <v>40.763742</v>
+        <v>40.7554749</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>-73.97019589999999</v>
+        <v>-73.9779336</v>
       </c>
       <c r="L27" s="13" t="inlineStr">
         <is>
@@ -2978,7 +2983,7 @@
       </c>
       <c r="M27" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1163 dentists</t>
         </is>
       </c>
       <c r="N27" s="13" t="inlineStr">
@@ -2993,17 +2998,17 @@
       </c>
       <c r="P27" s="13" t="inlineStr">
         <is>
-          <t>Since 2018</t>
+          <t>Since 1998</t>
         </is>
       </c>
       <c r="Q27" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram</t>
+          <t>Facebook, Instagram, LinkedIn</t>
         </is>
       </c>
       <c r="R27" s="13" t="inlineStr">
         <is>
-          <t>ZocDoc</t>
+          <t>ZocDoc, Digital Imaging</t>
         </is>
       </c>
       <c r="S27" s="12" t="n">
@@ -3015,23 +3020,23 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="20" customHeight="1">
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="9" t="n">
         <v>25</v>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>My NYC Dentist - 34th Street Dental</t>
+          <t>Midtown Dental Group Upper East Side</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>(212) 564-8164</t>
+          <t>(212) 588-1809</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>225 W 35th St #2, New York, NY 10001, USA</t>
+          <t>30 E 60th St Ste 2402, New York, NY 10022, USA</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -3041,25 +3046,25 @@
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>http://www.mynyc-dentist.com/</t>
+          <t>https://midtowndentalgroup.com/locations/uppereastside/</t>
         </is>
       </c>
       <c r="G28" s="9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>Monday: 8:30 AM – 6:00 PM</t>
+          <t>Monday: 9:00 AM – 5:00 PM</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>40.7522776</v>
+        <v>40.763742</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>-73.991056</v>
+        <v>-73.97019589999999</v>
       </c>
       <c r="L28" s="10" t="inlineStr">
         <is>
@@ -3073,7 +3078,7 @@
       </c>
       <c r="N28" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O28" s="10" t="inlineStr">
@@ -3083,7 +3088,7 @@
       </c>
       <c r="P28" s="10" t="inlineStr">
         <is>
-          <t>Since 2009</t>
+          <t>Since 2018</t>
         </is>
       </c>
       <c r="Q28" s="10" t="inlineStr">
@@ -3105,23 +3110,23 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="20" customHeight="1">
+    <row r="29" ht="30" customHeight="1">
       <c r="A29" s="12" t="n">
         <v>26</v>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Group Health Dental</t>
+          <t>My NYC Dentist - 34th Street Dental</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>(332) 249-1842</t>
+          <t>(212) 564-8164</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>230 W 41st St 15th Floor, New York, NY 10036, USA</t>
+          <t>225 W 35th St #2, New York, NY 10001, USA</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
@@ -3131,29 +3136,29 @@
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>https://grouphealthdental.com/</t>
+          <t>http://www.mynyc-dentist.com/</t>
         </is>
       </c>
       <c r="G29" s="12" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>1531</v>
+        <v>498</v>
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 5:00 PM</t>
+          <t>Monday: 8:30 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J29" s="12" t="n">
-        <v>40.7557231</v>
+        <v>40.7522776</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>-73.9888607</v>
+        <v>-73.991056</v>
       </c>
       <c r="L29" s="13" t="inlineStr">
         <is>
-          <t>General Dentistry, Cosmetic, Orthodontics, Periodontics</t>
+          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
         </is>
       </c>
       <c r="M29" s="13" t="inlineStr">
@@ -3163,7 +3168,7 @@
       </c>
       <c r="N29" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O29" s="13" t="inlineStr">
@@ -3173,7 +3178,7 @@
       </c>
       <c r="P29" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Since 2009</t>
         </is>
       </c>
       <c r="Q29" s="13" t="inlineStr">
@@ -3183,7 +3188,7 @@
       </c>
       <c r="R29" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ZocDoc</t>
         </is>
       </c>
       <c r="S29" s="12" t="n">
@@ -3195,23 +3200,23 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="20" customHeight="1">
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="9" t="n">
         <v>27</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Manhattan Bridge Orthodontics</t>
+          <t>Group Health Dental</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>(212) 274-0477</t>
+          <t>(332) 249-1842</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>77 Bowery 6th Floor, New York, NY 10002, USA</t>
+          <t>230 W 41st St 15th Floor, New York, NY 10036, USA</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -3221,29 +3226,29 @@
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>https://www.manhattanbridgeortho.com/</t>
+          <t>https://grouphealthdental.com/</t>
         </is>
       </c>
       <c r="G30" s="9" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>1514</v>
+        <v>1531</v>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>Monday: 10:00 AM – 7:00 PM</t>
+          <t>Monday: 9:00 AM – 5:00 PM</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>40.71666949999999</v>
+        <v>40.7557231</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>-73.99553539999999</v>
+        <v>-73.9888607</v>
       </c>
       <c r="L30" s="10" t="inlineStr">
         <is>
-          <t>Orthodontics</t>
+          <t>General Dentistry, Cosmetic, Orthodontics, Periodontics</t>
         </is>
       </c>
       <c r="M30" s="10" t="inlineStr">
@@ -3258,7 +3263,7 @@
       </c>
       <c r="O30" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="P30" s="10" t="inlineStr">
@@ -3268,7 +3273,7 @@
       </c>
       <c r="Q30" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, YouTube</t>
+          <t>Facebook, Instagram</t>
         </is>
       </c>
       <c r="R30" s="10" t="inlineStr">
@@ -3285,23 +3290,23 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1">
+    <row r="31" ht="30" customHeight="1">
       <c r="A31" s="12" t="n">
         <v>28</v>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>iSmile Orthodontics - NYC</t>
+          <t>Manhattan Bridge Orthodontics</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>(646) 863-2181</t>
+          <t>(212) 274-0477</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>4779 Broadway, New York, NY 10034, USA</t>
+          <t>77 Bowery 6th Floor, New York, NY 10002, USA</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
@@ -3311,25 +3316,25 @@
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>https://ismileorthodontics.com/inwood/</t>
+          <t>https://www.manhattanbridgeortho.com/</t>
         </is>
       </c>
       <c r="G31" s="12" t="n">
         <v>4.9</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>1006</v>
+        <v>1514</v>
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 6:00 PM</t>
+          <t>Monday: 10:00 AM – 7:00 PM</t>
         </is>
       </c>
       <c r="J31" s="12" t="n">
-        <v>40.8659992</v>
+        <v>40.71666949999999</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>-73.92655979999999</v>
+        <v>-73.99553539999999</v>
       </c>
       <c r="L31" s="13" t="inlineStr">
         <is>
@@ -3343,7 +3348,7 @@
       </c>
       <c r="N31" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O31" s="13" t="inlineStr">
@@ -3358,12 +3363,12 @@
       </c>
       <c r="Q31" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, Twitter/X, LinkedIn, YouTube</t>
+          <t>Facebook, Instagram, YouTube</t>
         </is>
       </c>
       <c r="R31" s="13" t="inlineStr">
         <is>
-          <t>Patient Portal</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S31" s="12" t="n">
@@ -3375,23 +3380,23 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="20" customHeight="1">
+    <row r="32" ht="30" customHeight="1">
       <c r="A32" s="9" t="n">
         <v>29</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>NYC Orthodontics</t>
+          <t>iSmile Orthodontics - NYC</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>(212) 245-5121</t>
+          <t>(646) 863-2181</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>30 Central Park S RM 2A, New York, NY 10019, USA</t>
+          <t>4779 Broadway, New York, NY 10034, USA</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -3401,29 +3406,29 @@
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>https://www.orthonyc.com/</t>
+          <t>https://ismileorthodontics.com/inwood/</t>
         </is>
       </c>
       <c r="G32" s="9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>54</v>
+        <v>1006</v>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>Monday: 12:00 – 6:30 PM</t>
+          <t>Monday: 9:00 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>40.7649517</v>
+        <v>40.8659992</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>-73.9750827</v>
+        <v>-73.92655979999999</v>
       </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
-          <t>Cosmetic, Orthodontics, Endodontics</t>
+          <t>Orthodontics</t>
         </is>
       </c>
       <c r="M32" s="10" t="inlineStr">
@@ -3433,12 +3438,12 @@
       </c>
       <c r="N32" s="10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O32" s="10" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P32" s="10" t="inlineStr">
@@ -3448,12 +3453,12 @@
       </c>
       <c r="Q32" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Facebook, Instagram, Twitter/X, LinkedIn, YouTube</t>
         </is>
       </c>
       <c r="R32" s="10" t="inlineStr">
         <is>
-          <t>ZocDoc, Digital Imaging</t>
+          <t>Patient Portal</t>
         </is>
       </c>
       <c r="S32" s="9" t="n">
@@ -3465,23 +3470,23 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1">
+    <row r="33" ht="30" customHeight="1">
       <c r="A33" s="12" t="n">
         <v>30</v>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Brite Orthodontics - Harlem (Central Park North Orthodontics)</t>
+          <t>NYC Orthodontics</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>(212) 866-9800</t>
+          <t>(212) 245-5121</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>1851 Adam Clayton Powell Jr Blvd, New York, NY 10026, USA</t>
+          <t>30 Central Park S RM 2A, New York, NY 10019, USA</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
@@ -3491,29 +3496,29 @@
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>https://www.briteorthodontics.com/locations/newyork-ny/</t>
+          <t>https://www.orthonyc.com/</t>
         </is>
       </c>
       <c r="G33" s="12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>673</v>
+        <v>54</v>
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 5:00 PM</t>
+          <t>Monday: 12:00 – 6:30 PM</t>
         </is>
       </c>
       <c r="J33" s="12" t="n">
-        <v>40.8009348</v>
+        <v>40.7649517</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>-73.95373900000001</v>
+        <v>-73.9750827</v>
       </c>
       <c r="L33" s="13" t="inlineStr">
         <is>
-          <t>General Dentistry, Orthodontics, Periodontics, Emergency</t>
+          <t>Cosmetic, Orthodontics, Endodontics</t>
         </is>
       </c>
       <c r="M33" s="13" t="inlineStr">
@@ -3538,12 +3543,12 @@
       </c>
       <c r="Q33" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, LinkedIn</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R33" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ZocDoc, Digital Imaging</t>
         </is>
       </c>
       <c r="S33" s="12" t="n">
@@ -3555,23 +3560,23 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
+    <row r="34" ht="30" customHeight="1">
       <c r="A34" s="9" t="n">
         <v>31</v>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Goodman Orthodontics</t>
+          <t>Brite Orthodontics - Harlem (Central Park North Orthodontics)</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>(212) 688-4663</t>
+          <t>(212) 866-9800</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>440 E 57th St B, New York, NY 10022, USA</t>
+          <t>1851 Adam Clayton Powell Jr Blvd, New York, NY 10026, USA</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -3581,29 +3586,29 @@
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>http://www.goodortho.com/</t>
+          <t>https://www.briteorthodontics.com/locations/newyork-ny/</t>
         </is>
       </c>
       <c r="G34" s="9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>275</v>
+        <v>673</v>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>Monday: 8:00 AM – 4:00 PM</t>
+          <t>Monday: 9:00 AM – 5:00 PM</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>40.7575229</v>
+        <v>40.8009348</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>-73.9616418</v>
+        <v>-73.95373900000001</v>
       </c>
       <c r="L34" s="10" t="inlineStr">
         <is>
-          <t>Orthodontics</t>
+          <t>General Dentistry, Orthodontics, Periodontics, Emergency</t>
         </is>
       </c>
       <c r="M34" s="10" t="inlineStr">
@@ -3613,7 +3618,7 @@
       </c>
       <c r="N34" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O34" s="10" t="inlineStr">
@@ -3628,7 +3633,7 @@
       </c>
       <c r="Q34" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, YouTube, TikTok</t>
+          <t>Facebook, Instagram, LinkedIn</t>
         </is>
       </c>
       <c r="R34" s="10" t="inlineStr">
@@ -3645,23 +3650,23 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1">
+    <row r="35" ht="30" customHeight="1">
       <c r="A35" s="12" t="n">
         <v>32</v>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Gramercy Orthodontics</t>
+          <t>Goodman Orthodontics</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>(212) 777-9177</t>
+          <t>(212) 688-4663</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>200 E 15th St STE PRB, New York, NY 10003, USA</t>
+          <t>440 E 57th St B, New York, NY 10022, USA</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
@@ -3671,25 +3676,25 @@
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>https://gramercyorthonyc.com/</t>
+          <t>http://www.goodortho.com/</t>
         </is>
       </c>
       <c r="G35" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>161</v>
+        <v>275</v>
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>Monday: 10:00 AM – 7:00 PM</t>
+          <t>Monday: 8:00 AM – 4:00 PM</t>
         </is>
       </c>
       <c r="J35" s="12" t="n">
-        <v>40.7337844</v>
+        <v>40.7575229</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>-73.98647919999999</v>
+        <v>-73.9616418</v>
       </c>
       <c r="L35" s="13" t="inlineStr">
         <is>
@@ -3718,7 +3723,7 @@
       </c>
       <c r="Q35" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram</t>
+          <t>Facebook, Instagram, YouTube, TikTok</t>
         </is>
       </c>
       <c r="R35" s="13" t="inlineStr">
@@ -3735,23 +3740,23 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="20" customHeight="1">
+    <row r="36" ht="30" customHeight="1">
       <c r="A36" s="9" t="n">
         <v>33</v>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Bronsky Orthodontics</t>
+          <t>Gramercy Orthodontics</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>(212) 758-0040</t>
+          <t>(212) 777-9177</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>530 Park Ave APT 1G, New York, NY 10065, USA</t>
+          <t>200 E 15th St STE PRB, New York, NY 10003, USA</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -3761,25 +3766,25 @@
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>http://www.bronskyorthodontics.com/?utm_source=GMBlisting&amp;utm_medium=organic</t>
+          <t>https://gramercyorthonyc.com/</t>
         </is>
       </c>
       <c r="G36" s="9" t="n">
         <v>5</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>481</v>
+        <v>161</v>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>Monday: 8:00 AM – 5:00 PM</t>
+          <t>Monday: 10:00 AM – 7:00 PM</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>40.7641462</v>
+        <v>40.7337844</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>-73.96946849999999</v>
+        <v>-73.98647919999999</v>
       </c>
       <c r="L36" s="10" t="inlineStr">
         <is>
@@ -3798,7 +3803,7 @@
       </c>
       <c r="O36" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="P36" s="10" t="inlineStr">
@@ -3808,7 +3813,7 @@
       </c>
       <c r="Q36" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, YouTube</t>
+          <t>Facebook, Instagram</t>
         </is>
       </c>
       <c r="R36" s="10" t="inlineStr">
@@ -3825,23 +3830,23 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="20" customHeight="1">
+    <row r="37" ht="30" customHeight="1">
       <c r="A37" s="12" t="n">
         <v>34</v>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Manhattan EastSide Orthodontics</t>
+          <t>Bronsky Orthodontics</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>(212) 289-8989</t>
+          <t>(212) 758-0040</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>207 E 94th St #501, New York, NY 10128, USA</t>
+          <t>530 Park Ave APT 1G, New York, NY 10065, USA</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
@@ -3851,29 +3856,29 @@
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>https://manhattaneastsideorthodontics.com/</t>
+          <t>http://www.bronskyorthodontics.com/?utm_source=GMBlisting&amp;utm_medium=organic</t>
         </is>
       </c>
       <c r="G37" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>429</v>
+        <v>481</v>
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 5:00 PM</t>
+          <t>Monday: 8:00 AM – 5:00 PM</t>
         </is>
       </c>
       <c r="J37" s="12" t="n">
-        <v>40.783778</v>
+        <v>40.7641462</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>-73.949438</v>
+        <v>-73.96946849999999</v>
       </c>
       <c r="L37" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Orthodontics</t>
         </is>
       </c>
       <c r="M37" s="13" t="inlineStr">
@@ -3898,7 +3903,7 @@
       </c>
       <c r="Q37" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Facebook, Instagram, YouTube</t>
         </is>
       </c>
       <c r="R37" s="13" t="inlineStr">
@@ -3915,23 +3920,23 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
+    <row r="38" ht="30" customHeight="1">
       <c r="A38" s="9" t="n">
         <v>35</v>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Smile Pop - Dr. Courtney Barry Orthodontist</t>
+          <t>Manhattan EastSide Orthodontics</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>(646) 770-2091</t>
+          <t>(212) 289-8989</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>76 Madison Ave, New York, NY 10016, USA</t>
+          <t>207 E 94th St #501, New York, NY 10128, USA</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -3941,29 +3946,29 @@
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>http://www.smilepop.com/</t>
+          <t>https://manhattaneastsideorthodontics.com/</t>
         </is>
       </c>
       <c r="G38" s="9" t="n">
         <v>5</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>Monday: 10:00 AM – 4:00 PM</t>
+          <t>Monday: 9:00 AM – 5:00 PM</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>40.74397099999999</v>
+        <v>40.783778</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>-73.9860561</v>
+        <v>-73.949438</v>
       </c>
       <c r="L38" s="10" t="inlineStr">
         <is>
-          <t>Cosmetic, Orthodontics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M38" s="10" t="inlineStr">
@@ -3973,7 +3978,7 @@
       </c>
       <c r="N38" s="10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O38" s="10" t="inlineStr">
@@ -3988,7 +3993,7 @@
       </c>
       <c r="Q38" s="10" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R38" s="10" t="inlineStr">
@@ -4005,23 +4010,23 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="20" customHeight="1">
+    <row r="39" ht="30" customHeight="1">
       <c r="A39" s="12" t="n">
         <v>36</v>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Salzer Orthodontics, Dr. Jennifer Salzer</t>
+          <t>Smile Pop - Dr. Courtney Barry Orthodontist</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>(212) 755-2333</t>
+          <t>(646) 770-2091</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>553 Park Ave, New York, NY 10065, USA</t>
+          <t>76 Madison Ave, New York, NY 10016, USA</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
@@ -4031,29 +4036,29 @@
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>https://lsortho.com/contact-orthodontist-nyc</t>
+          <t>http://www.smilepop.com/</t>
         </is>
       </c>
       <c r="G39" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>177</v>
+        <v>444</v>
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 6:00 PM</t>
+          <t>Monday: 10:00 AM – 4:00 PM</t>
         </is>
       </c>
       <c r="J39" s="12" t="n">
-        <v>40.7645406</v>
+        <v>40.74397099999999</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>-73.9683215</v>
+        <v>-73.9860561</v>
       </c>
       <c r="L39" s="13" t="inlineStr">
         <is>
-          <t>Orthodontics</t>
+          <t>Cosmetic, Orthodontics</t>
         </is>
       </c>
       <c r="M39" s="13" t="inlineStr">
@@ -4063,7 +4068,7 @@
       </c>
       <c r="N39" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O39" s="13" t="inlineStr">
@@ -4078,7 +4083,7 @@
       </c>
       <c r="Q39" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, LinkedIn, YouTube, TikTok</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="R39" s="13" t="inlineStr">
@@ -4087,7 +4092,7 @@
         </is>
       </c>
       <c r="S39" s="12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="T39" s="11" t="inlineStr">
         <is>
@@ -4095,55 +4100,55 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="20" customHeight="1">
+    <row r="40" ht="30" customHeight="1">
       <c r="A40" s="9" t="n">
         <v>37</v>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Jackson Heights Orthodontics</t>
+          <t>Salzer Orthodontics, Dr. Jennifer Salzer</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>(718) 335-4444</t>
+          <t>(212) 755-2333</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>37-43 77th St, Jackson Heights, NY 11372, USA</t>
+          <t>553 Park Ave, New York, NY 10065, USA</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>Jackson Heights</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>http://jhoortho.com/</t>
+          <t>https://lsortho.com/contact-orthodontist-nyc</t>
         </is>
       </c>
       <c r="G40" s="9" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>1337</v>
+        <v>177</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 5:00 PM</t>
+          <t>Monday: 9:00 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>40.7479692</v>
+        <v>40.7645406</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>-73.88860989999999</v>
+        <v>-73.9683215</v>
       </c>
       <c r="L40" s="10" t="inlineStr">
         <is>
-          <t>Cosmetic, Orthodontics</t>
+          <t>Orthodontics</t>
         </is>
       </c>
       <c r="M40" s="10" t="inlineStr">
@@ -4153,7 +4158,7 @@
       </c>
       <c r="N40" s="10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O40" s="10" t="inlineStr">
@@ -4168,16 +4173,16 @@
       </c>
       <c r="Q40" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram</t>
+          <t>Facebook, Instagram, LinkedIn, YouTube, TikTok</t>
         </is>
       </c>
       <c r="R40" s="10" t="inlineStr">
         <is>
-          <t>Teledentistry</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S40" s="9" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="T40" s="11" t="inlineStr">
         <is>
@@ -4185,40 +4190,40 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="20" customHeight="1">
+    <row r="41" ht="30" customHeight="1">
       <c r="A41" s="12" t="n">
         <v>38</v>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Wall Street Orthodontics</t>
+          <t>Jackson Heights Orthodontics</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>(212) 871-9835</t>
+          <t>(718) 335-4444</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>111 Broadway APT 1707, New York, NY 10006, USA</t>
+          <t>37-43 77th St, Jackson Heights, NY 11372, USA</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Jackson Heights</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>http://wallstreetortho.com/</t>
+          <t>http://jhoortho.com/</t>
         </is>
       </c>
       <c r="G41" s="12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>87</v>
+        <v>1337</v>
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
@@ -4226,14 +4231,14 @@
         </is>
       </c>
       <c r="J41" s="12" t="n">
-        <v>40.7086853</v>
+        <v>40.7479692</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>-74.01154869999999</v>
+        <v>-73.88860989999999</v>
       </c>
       <c r="L41" s="13" t="inlineStr">
         <is>
-          <t>Orthodontics</t>
+          <t>Cosmetic, Orthodontics</t>
         </is>
       </c>
       <c r="M41" s="13" t="inlineStr">
@@ -4243,7 +4248,7 @@
       </c>
       <c r="N41" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O41" s="13" t="inlineStr">
@@ -4258,16 +4263,16 @@
       </c>
       <c r="Q41" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, YouTube</t>
+          <t>Facebook, Instagram</t>
         </is>
       </c>
       <c r="R41" s="13" t="inlineStr">
         <is>
-          <t>Teledentistry, Digital Imaging</t>
+          <t>Teledentistry</t>
         </is>
       </c>
       <c r="S41" s="12" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="T41" s="11" t="inlineStr">
         <is>
@@ -4275,23 +4280,23 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="20" customHeight="1">
+    <row r="42" ht="30" customHeight="1">
       <c r="A42" s="9" t="n">
         <v>39</v>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Fellow Orthodontist</t>
+          <t>Wall Street Orthodontics</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>(917) 451-2999</t>
+          <t>(212) 871-9835</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>49 E 18th St, New York, NY 10003, USA</t>
+          <t>111 Broadway APT 1707, New York, NY 10006, USA</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -4301,29 +4306,29 @@
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>https://felloworthodontist.com/</t>
+          <t>http://wallstreetortho.com/</t>
         </is>
       </c>
       <c r="G42" s="9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>234</v>
+        <v>87</v>
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
-          <t>Monday: 10:00 AM – 5:00 PM</t>
+          <t>Monday: 9:00 AM – 5:00 PM</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>40.7375877</v>
+        <v>40.7086853</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>-73.98918399999999</v>
+        <v>-74.01154869999999</v>
       </c>
       <c r="L42" s="10" t="inlineStr">
         <is>
-          <t>Cosmetic, Orthodontics</t>
+          <t>Orthodontics</t>
         </is>
       </c>
       <c r="M42" s="10" t="inlineStr">
@@ -4333,12 +4338,12 @@
       </c>
       <c r="N42" s="10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O42" s="10" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P42" s="10" t="inlineStr">
@@ -4348,16 +4353,16 @@
       </c>
       <c r="Q42" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, Twitter/X</t>
+          <t>Facebook, Instagram, YouTube</t>
         </is>
       </c>
       <c r="R42" s="10" t="inlineStr">
         <is>
-          <t>Teledentistry</t>
+          <t>Teledentistry, Digital Imaging</t>
         </is>
       </c>
       <c r="S42" s="9" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="T42" s="11" t="inlineStr">
         <is>
@@ -4365,23 +4370,23 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="20" customHeight="1">
+    <row r="43" ht="30" customHeight="1">
       <c r="A43" s="12" t="n">
         <v>40</v>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Straight Set Orthodontics | Harlem</t>
+          <t>Fellow Orthodontist</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>(212) 996-7300</t>
+          <t>(917) 451-2999</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>241 Malcolm X Blvd, New York, NY 10027, USA</t>
+          <t>49 E 18th St, New York, NY 10003, USA</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
@@ -4391,25 +4396,25 @@
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>https://www.straightsetortho.com/harlem</t>
+          <t>https://felloworthodontist.com/</t>
         </is>
       </c>
       <c r="G43" s="12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>677</v>
+        <v>234</v>
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 6:00 PM</t>
+          <t>Monday: 10:00 AM – 5:00 PM</t>
         </is>
       </c>
       <c r="J43" s="12" t="n">
-        <v>40.8060963</v>
+        <v>40.7375877</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>-73.94716439999999</v>
+        <v>-73.98918399999999</v>
       </c>
       <c r="L43" s="13" t="inlineStr">
         <is>
@@ -4438,7 +4443,7 @@
       </c>
       <c r="Q43" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram</t>
+          <t>Facebook, Instagram, Twitter/X</t>
         </is>
       </c>
       <c r="R43" s="13" t="inlineStr">
@@ -4455,23 +4460,23 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="20" customHeight="1">
+    <row r="44" ht="30" customHeight="1">
       <c r="A44" s="9" t="n">
         <v>41</v>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Central Park Orthodontics</t>
+          <t>Straight Set Orthodontics | Harlem</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>(212) 362-4400</t>
+          <t>(212) 996-7300</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>271A Central Park West, (entrance on, W 87th St, New York, NY 10024, USA</t>
+          <t>241 Malcolm X Blvd, New York, NY 10027, USA</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -4481,14 +4486,14 @@
       </c>
       <c r="F44" s="9" t="inlineStr">
         <is>
-          <t>https://www.centralparkorthodontics.com/</t>
+          <t>https://www.straightsetortho.com/harlem</t>
         </is>
       </c>
       <c r="G44" s="9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>60</v>
+        <v>677</v>
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
@@ -4496,14 +4501,14 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>40.786237</v>
+        <v>40.8060963</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>-73.969014</v>
+        <v>-73.94716439999999</v>
       </c>
       <c r="L44" s="10" t="inlineStr">
         <is>
-          <t>Orthodontics</t>
+          <t>Cosmetic, Orthodontics</t>
         </is>
       </c>
       <c r="M44" s="10" t="inlineStr">
@@ -4513,7 +4518,7 @@
       </c>
       <c r="N44" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O44" s="10" t="inlineStr">
@@ -4523,7 +4528,7 @@
       </c>
       <c r="P44" s="10" t="inlineStr">
         <is>
-          <t>Since 2006</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q44" s="10" t="inlineStr">
@@ -4533,11 +4538,11 @@
       </c>
       <c r="R44" s="10" t="inlineStr">
         <is>
-          <t>ZocDoc</t>
+          <t>Teledentistry</t>
         </is>
       </c>
       <c r="S44" s="9" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="T44" s="11" t="inlineStr">
         <is>
@@ -4545,23 +4550,23 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="20" customHeight="1">
+    <row r="45" ht="30" customHeight="1">
       <c r="A45" s="12" t="n">
         <v>42</v>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Gibbs Orthodontic Associates, P.C : Invisalign, Braces and Dentofacial Orthopedics</t>
+          <t>Central Park Orthodontics</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>(212) 535-4111</t>
+          <t>(212) 362-4400</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>40 E 84th St, New York, NY 10028, USA</t>
+          <t>271A Central Park West, (entrance on, W 87th St, New York, NY 10024, USA</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
@@ -4571,29 +4576,29 @@
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>https://www.gibbsortho.com/</t>
+          <t>https://www.centralparkorthodontics.com/</t>
         </is>
       </c>
       <c r="G45" s="12" t="n">
         <v>4.9</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>186</v>
+        <v>60</v>
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 5:00 PM</t>
+          <t>Monday: 9:00 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J45" s="12" t="n">
-        <v>40.7793093</v>
+        <v>40.786237</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>-73.95947029999999</v>
+        <v>-73.969014</v>
       </c>
       <c r="L45" s="13" t="inlineStr">
         <is>
-          <t>General Dentistry, Cosmetic, Orthodontics</t>
+          <t>Orthodontics</t>
         </is>
       </c>
       <c r="M45" s="13" t="inlineStr">
@@ -4603,31 +4608,31 @@
       </c>
       <c r="N45" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O45" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="P45" s="13" t="inlineStr">
         <is>
-          <t>Since 1985</t>
+          <t>Since 2006</t>
         </is>
       </c>
       <c r="Q45" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, Twitter/X, LinkedIn, YouTube, TikTok</t>
+          <t>Facebook, Instagram</t>
         </is>
       </c>
       <c r="R45" s="13" t="inlineStr">
         <is>
-          <t>Teledentistry, Digital Imaging</t>
+          <t>ZocDoc</t>
         </is>
       </c>
       <c r="S45" s="12" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="T45" s="11" t="inlineStr">
         <is>
@@ -4635,23 +4640,23 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="20" customHeight="1">
+    <row r="46" ht="30" customHeight="1">
       <c r="A46" s="9" t="n">
         <v>43</v>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Manhattan Family Orthodontics-Uptown</t>
+          <t>Gibbs Orthodontic Associates, P.C : Invisalign, Braces and Dentofacial Orthopedics</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>(347) 767-5668</t>
+          <t>(212) 535-4111</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>207 E 63rd St, New York, NY 10022, USA</t>
+          <t>40 E 84th St, New York, NY 10028, USA</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
@@ -4661,29 +4666,29 @@
       </c>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>https://www.manhattanfamilyorthodontics.com/</t>
+          <t>https://www.gibbsortho.com/</t>
         </is>
       </c>
       <c r="G46" s="9" t="n">
         <v>4.9</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
-          <t>Monday: 1:00 – 6:00 PM</t>
+          <t>Monday: 9:00 AM – 5:00 PM</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>40.7640232</v>
+        <v>40.7793093</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>-73.96417579999999</v>
+        <v>-73.95947029999999</v>
       </c>
       <c r="L46" s="10" t="inlineStr">
         <is>
-          <t>General Dentistry, Orthodontics</t>
+          <t>General Dentistry, Cosmetic, Orthodontics</t>
         </is>
       </c>
       <c r="M46" s="10" t="inlineStr">
@@ -4693,27 +4698,27 @@
       </c>
       <c r="N46" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O46" s="10" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P46" s="10" t="inlineStr">
         <is>
-          <t>Since 2019</t>
+          <t>Since 1985</t>
         </is>
       </c>
       <c r="Q46" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram</t>
+          <t>Facebook, Instagram, Twitter/X, LinkedIn, YouTube, TikTok</t>
         </is>
       </c>
       <c r="R46" s="10" t="inlineStr">
         <is>
-          <t>ZocDoc, Teledentistry</t>
+          <t>Teledentistry, Digital Imaging</t>
         </is>
       </c>
       <c r="S46" s="9" t="n">
@@ -4725,23 +4730,23 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="20" customHeight="1">
+    <row r="47" ht="30" customHeight="1">
       <c r="A47" s="12" t="n">
         <v>44</v>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Lemchen Salzer Orthodontics</t>
+          <t>Orthodontics Center of NYC</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>(212) 755-2333</t>
+          <t>(646) 491-7133</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>553 Park Ave, New York, NY 10065, USA</t>
+          <t>263 West End Ave Fl 1, New York, NY 10023, USA</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
@@ -4751,14 +4756,14 @@
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>http://www.lsortho.com/</t>
+          <t>https://www.orthodonticscenternyc.com/</t>
         </is>
       </c>
       <c r="G47" s="12" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>313</v>
+        <v>12</v>
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
@@ -4766,10 +4771,10 @@
         </is>
       </c>
       <c r="J47" s="12" t="n">
-        <v>40.76448</v>
+        <v>40.7800807</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>-73.96826279999999</v>
+        <v>-73.9845136</v>
       </c>
       <c r="L47" s="13" t="inlineStr">
         <is>
@@ -4788,50 +4793,50 @@
       </c>
       <c r="O47" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="P47" s="13" t="inlineStr">
         <is>
-          <t>Since 1974</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q47" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, LinkedIn, YouTube, TikTok</t>
+          <t>Facebook, Instagram, Twitter/X, LinkedIn</t>
         </is>
       </c>
       <c r="R47" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Teledentistry</t>
         </is>
       </c>
       <c r="S47" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="T47" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
+        <v>68</v>
+      </c>
+      <c r="T47" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
       <c r="A48" s="9" t="n">
         <v>45</v>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Orthodontics Center of NYC</t>
+          <t>Lemchen Salzer Orthodontics</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>(646) 491-7133</t>
+          <t>(212) 755-2333</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>263 West End Ave Fl 1, New York, NY 10023, USA</t>
+          <t>553 Park Ave, New York, NY 10065, USA</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -4841,14 +4846,14 @@
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>https://www.orthodonticscenternyc.com/</t>
+          <t>http://www.lsortho.com/</t>
         </is>
       </c>
       <c r="G48" s="9" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>12</v>
+        <v>313</v>
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
@@ -4856,10 +4861,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>40.7800807</v>
+        <v>40.76448</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>-73.9845136</v>
+        <v>-73.96826279999999</v>
       </c>
       <c r="L48" s="10" t="inlineStr">
         <is>
@@ -4878,50 +4883,50 @@
       </c>
       <c r="O48" s="10" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P48" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Since 1974</t>
         </is>
       </c>
       <c r="Q48" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, Twitter/X, LinkedIn</t>
+          <t>Facebook, Instagram, LinkedIn, YouTube, TikTok</t>
         </is>
       </c>
       <c r="R48" s="10" t="inlineStr">
         <is>
-          <t>Teledentistry</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S48" s="9" t="n">
-        <v>68</v>
-      </c>
-      <c r="T48" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
+        <v>100</v>
+      </c>
+      <c r="T48" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
       <c r="A49" s="12" t="n">
         <v>46</v>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Mid-Manhattan Oral Surgery, PC</t>
+          <t>Manhattan Family Orthodontics-Uptown</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>(212) 918-1859</t>
+          <t>(347) 767-5668</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>36 West 44th Street, Suite 600 Between, 5th and 6th Avenue, New York, NY 10036, USA</t>
+          <t>207 E 63rd St, New York, NY 10022, USA</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
@@ -4931,29 +4936,29 @@
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>https://www.midmanhattanoralsurgery.com/</t>
+          <t>https://www.manhattanfamilyorthodontics.com/</t>
         </is>
       </c>
       <c r="G49" s="12" t="n">
         <v>4.9</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>895</v>
+        <v>159</v>
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>Monday: 8:00 AM – 5:00 PM</t>
+          <t>Monday: 1:00 – 6:00 PM</t>
         </is>
       </c>
       <c r="J49" s="12" t="n">
-        <v>40.7555517</v>
+        <v>40.7640232</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>-73.9819631</v>
+        <v>-73.96417579999999</v>
       </c>
       <c r="L49" s="13" t="inlineStr">
         <is>
-          <t>Implants, Oral Surgery</t>
+          <t>General Dentistry, Orthodontics</t>
         </is>
       </c>
       <c r="M49" s="13" t="inlineStr">
@@ -4963,27 +4968,27 @@
       </c>
       <c r="N49" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O49" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="P49" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Since 2019</t>
         </is>
       </c>
       <c r="Q49" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Facebook, Instagram</t>
         </is>
       </c>
       <c r="R49" s="13" t="inlineStr">
         <is>
-          <t>Digital Imaging</t>
+          <t>ZocDoc, Teledentistry</t>
         </is>
       </c>
       <c r="S49" s="12" t="n">
@@ -4995,23 +5000,23 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="20" customHeight="1">
+    <row r="50" ht="30" customHeight="1">
       <c r="A50" s="9" t="n">
         <v>47</v>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>New York Oral &amp; Maxillofacial Surgery &amp; Dental Implant Center</t>
+          <t>Mid-Manhattan Oral Surgery, PC</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>(646) 681-7068</t>
+          <t>(212) 918-1859</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>800B 5th Ave Ste 1, New York, NY 10065, USA</t>
+          <t>36 West 44th Street, Suite 600 Between, 5th and 6th Avenue, New York, NY 10036, USA</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
@@ -5021,29 +5026,29 @@
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>https://www.new-york-oral-surgery.com/</t>
+          <t>https://www.midmanhattanoralsurgery.com/</t>
         </is>
       </c>
       <c r="G50" s="9" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>12</v>
+        <v>895</v>
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 5:00 PM</t>
+          <t>Monday: 8:00 AM – 5:00 PM</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>40.7655359</v>
+        <v>40.7555517</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>-73.97173069999999</v>
+        <v>-73.9819631</v>
       </c>
       <c r="L50" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Implants, Oral Surgery</t>
         </is>
       </c>
       <c r="M50" s="10" t="inlineStr">
@@ -5053,7 +5058,7 @@
       </c>
       <c r="N50" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O50" s="10" t="inlineStr">
@@ -5073,30 +5078,30 @@
       </c>
       <c r="R50" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Digital Imaging</t>
         </is>
       </c>
       <c r="S50" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="T50" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
+        <v>100</v>
+      </c>
+      <c r="T50" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
       <c r="A51" s="12" t="n">
         <v>48</v>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>David A. Koslovsky, DDS, FACS, FACD</t>
+          <t>New York Oral &amp; Maxillofacial Surgery &amp; Dental Implant Center</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>(212) 888-4760</t>
+          <t>(646) 681-7068</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
@@ -5111,14 +5116,14 @@
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>https://www.new-york-oral-surgery.com/oral-surgeon-ny/oral-surgeon-new-york-city.htm</t>
+          <t>https://www.new-york-oral-surgery.com/</t>
         </is>
       </c>
       <c r="G51" s="12" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>146</v>
+        <v>12</v>
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
@@ -5167,63 +5172,63 @@
         </is>
       </c>
       <c r="S51" s="12" t="n">
-        <v>93</v>
-      </c>
-      <c r="T51" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
+        <v>45</v>
+      </c>
+      <c r="T51" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
       <c r="A52" s="9" t="n">
         <v>49</v>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Dental Oral Surgery</t>
+          <t>Oral Surgery of Northern New York</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>(347) 590-9910</t>
+          <t>(315) 786-3990</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>2403 Grand Concourse, Bronx, NY 10468, USA</t>
+          <t>163 S Bellew Ave, Watertown, NY 13601, USA</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Watertown</t>
         </is>
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>http://www.mofsny.com/</t>
+          <t>https://www.oralsurgerynny.com/</t>
         </is>
       </c>
       <c r="G52" s="9" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>583</v>
+        <v>994</v>
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
-          <t>Monday: 7:30 AM – 1:00 PM</t>
+          <t>Monday: 7:30 AM – 4:30 PM</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>40.8603366</v>
+        <v>43.9743256</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>-73.89870549999999</v>
+        <v>-75.9319438</v>
       </c>
       <c r="L52" s="10" t="inlineStr">
         <is>
-          <t>General Dentistry, Implants, Oral Surgery, Prosthodontics</t>
+          <t>Implants, Oral Surgery</t>
         </is>
       </c>
       <c r="M52" s="10" t="inlineStr">
@@ -5233,7 +5238,7 @@
       </c>
       <c r="N52" s="10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O52" s="10" t="inlineStr">
@@ -5243,12 +5248,12 @@
       </c>
       <c r="P52" s="10" t="inlineStr">
         <is>
-          <t>Since 2010</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q52" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Facebook, Instagram, Twitter/X</t>
         </is>
       </c>
       <c r="R52" s="10" t="inlineStr">
@@ -5265,23 +5270,23 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="20" customHeight="1">
+    <row r="53" ht="30" customHeight="1">
       <c r="A53" s="12" t="n">
         <v>50</v>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>NYC Dental Implants Center</t>
+          <t>David A. Koslovsky, DDS, FACS, FACD</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>(212) 256-0000</t>
+          <t>(212) 888-4760</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>121 E 60th St Ste 6C2, New York, NY 10065, USA</t>
+          <t>800B 5th Ave Ste 1, New York, NY 10065, USA</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
@@ -5291,29 +5296,29 @@
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>https://www.nycdentalimplantscenter.com/</t>
+          <t>https://www.new-york-oral-surgery.com/oral-surgeon-ny/oral-surgeon-new-york-city.htm</t>
         </is>
       </c>
       <c r="G53" s="12" t="n">
         <v>4.9</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>200</v>
+        <v>146</v>
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>Monday: 8:00 AM – 6:00 PM</t>
+          <t>Monday: 9:00 AM – 5:00 PM</t>
         </is>
       </c>
       <c r="J53" s="12" t="n">
-        <v>40.7632573</v>
+        <v>40.7655359</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>-73.96829579999999</v>
+        <v>-73.97173069999999</v>
       </c>
       <c r="L53" s="13" t="inlineStr">
         <is>
-          <t>Implants, Periodontics, Oral Surgery, Emergency</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M53" s="13" t="inlineStr">
@@ -5323,12 +5328,12 @@
       </c>
       <c r="N53" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O53" s="13" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P53" s="13" t="inlineStr">
@@ -5338,16 +5343,16 @@
       </c>
       <c r="Q53" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, Twitter/X, LinkedIn, YouTube, TikTok</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R53" s="13" t="inlineStr">
         <is>
-          <t>Digital Imaging</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S53" s="12" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="T53" s="11" t="inlineStr">
         <is>

--- a/output/New York_Dental_Clinics_Enriched.xlsx
+++ b/output/New York_Dental_Clinics_Enriched.xlsx
@@ -654,10 +654,10 @@
         <v>50</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
@@ -688,10 +688,10 @@
         <v>50</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0</v>
@@ -1136,17 +1136,17 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>New York Dental Office</t>
+          <t>ORAL Dental Studio NYC</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>(212) 548-3261</t>
+          <t>(646) 663-7633</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>245 E 63rd St #110, New York, NY 10065, USA</t>
+          <t>131 Essex St Fl 2, New York, NY 10002, USA</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -1156,25 +1156,25 @@
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>https://www.newyorkdentaloffice.com/</t>
+          <t>https://www.oraldentalstudio.com/</t>
         </is>
       </c>
       <c r="G7" s="12" t="n">
         <v>4.9</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>Monday: 8:30 AM – 5:00 PM</t>
+          <t>Monday: 9:00 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J7" s="12" t="n">
-        <v>40.7633351</v>
+        <v>40.7200496</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>-73.9627181</v>
+        <v>-73.98762359999999</v>
       </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="Q7" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Twitter/X</t>
+          <t>Facebook, Instagram, LinkedIn</t>
         </is>
       </c>
       <c r="R7" s="13" t="inlineStr">
         <is>
-          <t>ZocDoc</t>
+          <t>Digital Imaging, Laser Dentistry</t>
         </is>
       </c>
       <c r="S7" s="12" t="n">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>ORAL Dental Studio NYC</t>
+          <t>New York Dental Office</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>(646) 663-7633</t>
+          <t>(212) 548-3261</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>131 Essex St Fl 2, New York, NY 10002, USA</t>
+          <t>245 E 63rd St #110, New York, NY 10065, USA</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
@@ -1336,25 +1336,25 @@
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>https://www.oraldentalstudio.com/</t>
+          <t>https://www.newyorkdentaloffice.com/</t>
         </is>
       </c>
       <c r="G9" s="12" t="n">
         <v>4.9</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 6:00 PM</t>
+          <t>Monday: 8:30 AM – 5:00 PM</t>
         </is>
       </c>
       <c r="J9" s="12" t="n">
-        <v>40.7200496</v>
+        <v>40.7633351</v>
       </c>
       <c r="K9" s="12" t="n">
-        <v>-73.98762359999999</v>
+        <v>-73.9627181</v>
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="Q9" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, LinkedIn</t>
+          <t>Facebook, Twitter/X</t>
         </is>
       </c>
       <c r="R9" s="13" t="inlineStr">
         <is>
-          <t>Digital Imaging, Laser Dentistry</t>
+          <t>ZocDoc</t>
         </is>
       </c>
       <c r="S9" s="12" t="n">
@@ -1406,17 +1406,17 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Midtown Dental Group Fashion District</t>
+          <t>Pearl Dental NYC</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>(212) 730-4440</t>
+          <t>(212) 344-9317</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>241 W 37th St Ground Floor, New York, NY 10018, USA</t>
+          <t>233 Broadway 18 Suite 1801, New York, NY 10279, USA</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -1426,44 +1426,44 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>http://www.midtowndentalgroup.com/</t>
+          <t>https://www.pearldentalnyc.com/</t>
         </is>
       </c>
       <c r="G10" s="9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>734</v>
+        <v>475</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 5:45 PM</t>
+          <t>Monday: 8:00 AM – 5:00 PM</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>40.7538706</v>
+        <v>40.7123834</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>-73.9909457</v>
+        <v>-74.0079386</v>
       </c>
       <c r="L10" s="10" t="inlineStr">
         <is>
-          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
-          <t>4 dentists</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N10" s="10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O10" s="10" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P10" s="10" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R10" s="10" t="inlineStr">
         <is>
-          <t>ZocDoc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S10" s="9" t="n">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Pearl Dental NYC</t>
+          <t>Midtown Dental Care Associates</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>(212) 344-9317</t>
+          <t>(212) 685-4730</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>233 Broadway 18 Suite 1801, New York, NY 10279, USA</t>
+          <t>12 E 41st St Ste 1100, New York, NY 10017, USA</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -1516,29 +1516,29 @@
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>https://www.pearldentalnyc.com/</t>
+          <t>https://www.midtowndentalcareassociates.com/?utm_source=gmb&amp;utm_medium=organic</t>
         </is>
       </c>
       <c r="G11" s="12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>475</v>
+        <v>573</v>
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>Monday: 8:00 AM – 5:00 PM</t>
+          <t>Monday: 8:00 AM – 7:00 PM</t>
         </is>
       </c>
       <c r="J11" s="12" t="n">
-        <v>40.7123834</v>
+        <v>40.752382</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>-74.0079386</v>
+        <v>-73.980661</v>
       </c>
       <c r="L11" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
         </is>
       </c>
       <c r="M11" s="13" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="Q11" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Facebook, Instagram</t>
         </is>
       </c>
       <c r="R11" s="13" t="inlineStr">
@@ -1586,17 +1586,17 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Midtown Dental Care Associates</t>
+          <t>NYC Dental Center</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>(212) 685-4730</t>
+          <t>(646) 861-3070</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>12 E 41st St Ste 1100, New York, NY 10017, USA</t>
+          <t>216 E 39th St #1, New York, NY 10016, USA</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -1606,29 +1606,29 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>https://www.midtowndentalcareassociates.com/?utm_source=gmb&amp;utm_medium=organic</t>
+          <t>https://weence.com/dentists/new-york-1/nyc-dental-center/</t>
         </is>
       </c>
       <c r="G12" s="9" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>573</v>
+        <v>255</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>Monday: 8:00 AM – 7:00 PM</t>
+          <t>Monday: 10:00 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>40.752382</v>
+        <v>40.7483698</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>-73.980661</v>
+        <v>-73.9752108</v>
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
-          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
+          <t>General Dentistry, Cosmetic, Implants, Periodontics</t>
         </is>
       </c>
       <c r="M12" s="10" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="O12" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="P12" s="10" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="Q12" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R12" s="10" t="inlineStr">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>NYC Dental Center</t>
+          <t>NYC Smile Spa</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>(646) 861-3070</t>
+          <t>(646) 374-2242</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>216 E 39th St #1, New York, NY 10016, USA</t>
+          <t>30 E 60th St Ste 1201, New York, NY 10022, USA</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
@@ -1696,29 +1696,29 @@
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>https://weence.com/dentists/new-york-1/nyc-dental-center/</t>
+          <t>https://www.nycsmilespa.com/</t>
         </is>
       </c>
       <c r="G13" s="12" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>255</v>
+        <v>395</v>
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>Monday: 10:00 AM – 6:00 PM</t>
+          <t>Monday: 8:00 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J13" s="12" t="n">
-        <v>40.7483698</v>
+        <v>40.7637066</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>-73.9752108</v>
+        <v>-73.970242</v>
       </c>
       <c r="L13" s="13" t="inlineStr">
         <is>
-          <t>Implants, Periodontics, Endodontics, Oral Surgery</t>
+          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
         </is>
       </c>
       <c r="M13" s="13" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="O13" s="13" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P13" s="13" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="Q13" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Facebook, Instagram, YouTube</t>
         </is>
       </c>
       <c r="R13" s="13" t="inlineStr">
@@ -1766,17 +1766,17 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>NYC Smile Spa</t>
+          <t>212 Dental Care</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>(646) 374-2242</t>
+          <t>(888) 506-9583</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>30 E 60th St Ste 1201, New York, NY 10022, USA</t>
+          <t>286 Madison Ave 10th Floor, New York, NY 10017, USA</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -1786,29 +1786,29 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>https://www.nycsmilespa.com/</t>
+          <t>http://212dentalcare.com/</t>
         </is>
       </c>
       <c r="G14" s="9" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>395</v>
+        <v>3285</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>Monday: 8:00 AM – 6:00 PM</t>
+          <t>Monday: 8:00 AM – 8:00 PM</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>40.7637066</v>
+        <v>40.751693</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>-73.970242</v>
+        <v>-73.9803106</v>
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="N14" s="10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O14" s="10" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="Q14" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, YouTube</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R14" s="10" t="inlineStr">
@@ -1856,17 +1856,17 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>212 Dental Care</t>
+          <t>SoHo Dental Group NYC</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>(888) 506-9583</t>
+          <t>(212) 878-7646</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>286 Madison Ave 10th Floor, New York, NY 10017, USA</t>
+          <t>552 Broadway #505, New York, NY 10012, USA</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -1876,25 +1876,25 @@
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>http://212dentalcare.com/</t>
+          <t>https://www.sohodentalgroup.com/?utm_campaign=gmb&amp;utm_medium=organic&amp;utm_source=gmb</t>
         </is>
       </c>
       <c r="G15" s="12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>3285</v>
+        <v>540</v>
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>Monday: 8:00 AM – 8:00 PM</t>
+          <t>Monday: 9:00 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J15" s="12" t="n">
-        <v>40.751693</v>
+        <v>40.7237243</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>-73.9803106</v>
+        <v>-73.99803159999999</v>
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
@@ -1946,17 +1946,17 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>SoHo Dental Group NYC</t>
+          <t>Studio Smiles NYC</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>(212) 878-7646</t>
+          <t>(646) 470-1376</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>552 Broadway #505, New York, NY 10012, USA</t>
+          <t>41 Park Ave # 1C, New York, NY 10016, USA</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -1966,29 +1966,29 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>https://www.sohodentalgroup.com/?utm_campaign=gmb&amp;utm_medium=organic&amp;utm_source=gmb</t>
+          <t>http://www.studiosmilesnyc.com/</t>
         </is>
       </c>
       <c r="G16" s="9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>540</v>
+        <v>611</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 6:00 PM</t>
+          <t>Monday: 8:00 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>40.7237243</v>
+        <v>40.748366</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>-73.99803159999999</v>
+        <v>-73.97995039999999</v>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="N16" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O16" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="P16" s="10" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Q16" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Facebook, Instagram, Twitter/X</t>
         </is>
       </c>
       <c r="R16" s="10" t="inlineStr">
@@ -2036,17 +2036,17 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Studio Smiles NYC</t>
+          <t>Lumia Dental PLLC</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>(646) 470-1376</t>
+          <t>(212) 287-1275</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>41 Park Ave # 1C, New York, NY 10016, USA</t>
+          <t>160 Broadway #1004, New York, NY 10038, USA</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
@@ -2056,14 +2056,14 @@
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>http://www.studiosmilesnyc.com/</t>
+          <t>https://www.lumiadental.com/</t>
         </is>
       </c>
       <c r="G17" s="12" t="n">
         <v>4.9</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>611</v>
+        <v>768</v>
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
@@ -2071,14 +2071,14 @@
         </is>
       </c>
       <c r="J17" s="12" t="n">
-        <v>40.748366</v>
+        <v>40.70937199999999</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>-73.97995039999999</v>
+        <v>-74.00997500000001</v>
       </c>
       <c r="L17" s="13" t="inlineStr">
         <is>
-          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
+          <t>Cosmetic, Orthodontics, Periodontics, Endodontics</t>
         </is>
       </c>
       <c r="M17" s="13" t="inlineStr">
@@ -2093,22 +2093,22 @@
       </c>
       <c r="O17" s="13" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P17" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Since 2008</t>
         </is>
       </c>
       <c r="Q17" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, Twitter/X</t>
+          <t>Facebook, Instagram, Twitter/X, LinkedIn</t>
         </is>
       </c>
       <c r="R17" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ZocDoc</t>
         </is>
       </c>
       <c r="S17" s="12" t="n">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Lumia Dental PLLC</t>
+          <t>My NYC Dentist - Hudson Street Dental</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>(212) 287-1275</t>
+          <t>(212) 359-0064</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>160 Broadway #1004, New York, NY 10038, USA</t>
+          <t>90 Vandam St, New York, NY 10013, USA</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -2146,29 +2146,29 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>https://www.lumiadental.com/</t>
+          <t>https://www.mynyc-dentist.com/</t>
         </is>
       </c>
       <c r="G18" s="9" t="n">
         <v>4.9</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>768</v>
+        <v>289</v>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>Monday: 8:00 AM – 6:00 PM</t>
+          <t>Monday: 8:30 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>40.70937199999999</v>
+        <v>40.7265687</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>-74.00997500000001</v>
+        <v>-74.00812239999999</v>
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>Cosmetic, Orthodontics, Periodontics, Endodontics</t>
+          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr">
@@ -2178,22 +2178,22 @@
       </c>
       <c r="N18" s="10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O18" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="P18" s="10" t="inlineStr">
         <is>
-          <t>Since 2008</t>
+          <t>Since 2009</t>
         </is>
       </c>
       <c r="Q18" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, Twitter/X, LinkedIn</t>
+          <t>Facebook, Instagram</t>
         </is>
       </c>
       <c r="R18" s="10" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>My NYC Dentist - Hudson Street Dental</t>
+          <t>Diamond District Dental NYC - Midtown Dentist</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>(212) 359-0064</t>
+          <t>(212) 759-5595</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>90 Vandam St, New York, NY 10013, USA</t>
+          <t>10 W 46th St #1401, New York, NY 10036, USA</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
@@ -2236,29 +2236,29 @@
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>https://www.mynyc-dentist.com/</t>
+          <t>https://www.dddentalnyc.com/?utm_campaign=gmb</t>
         </is>
       </c>
       <c r="G19" s="12" t="n">
         <v>4.9</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>289</v>
+        <v>595</v>
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>Monday: 8:30 AM – 6:00 PM</t>
+          <t>Monday: 9:00 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J19" s="12" t="n">
-        <v>40.7265687</v>
+        <v>40.7563177</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>-74.00812239999999</v>
+        <v>-73.9800044</v>
       </c>
       <c r="L19" s="13" t="inlineStr">
         <is>
-          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M19" s="13" t="inlineStr">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="O19" s="13" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P19" s="13" t="inlineStr">
         <is>
-          <t>Since 2009</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q19" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R19" s="13" t="inlineStr">
         <is>
-          <t>ZocDoc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S19" s="12" t="n">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Diamond District Dental NYC - Midtown Dentist</t>
+          <t>City Dental Group NYC</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>(212) 759-5595</t>
+          <t>(212) 425-0505</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>10 W 46th St #1401, New York, NY 10036, USA</t>
+          <t>11 Broadway Lobby 4, New York, NY 10004, USA</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -2326,29 +2326,29 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>https://www.dddentalnyc.com/?utm_campaign=gmb</t>
+          <t>https://citydentalnyc.com/?utm_source=gbp&amp;utm_medium=organic&amp;utm_campaign=gbp-listing</t>
         </is>
       </c>
       <c r="G20" s="9" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>595</v>
+        <v>311</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 6:00 PM</t>
+          <t>Monday: 9:30 AM – 5:30 PM</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>40.7563177</v>
+        <v>40.7053407</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>-73.9800044</v>
+        <v>-74.01385759999999</v>
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
+          <t>Cosmetic, Implants, Orthodontics, Periodontics</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr">
@@ -2368,17 +2368,17 @@
       </c>
       <c r="P20" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Since 2006</t>
         </is>
       </c>
       <c r="Q20" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, YouTube, TikTok</t>
+          <t>Facebook, Instagram</t>
         </is>
       </c>
       <c r="R20" s="10" t="inlineStr">
         <is>
-          <t>ZocDoc, Laser Dentistry</t>
+          <t>Digital Imaging</t>
         </is>
       </c>
       <c r="S20" s="9" t="n">
@@ -2783,7 +2783,7 @@
         <v>4.9</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
-          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="O26" s="10" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P26" s="10" t="inlineStr">
@@ -2913,12 +2913,12 @@
       </c>
       <c r="Q26" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, YouTube</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R26" s="10" t="inlineStr">
         <is>
-          <t>Digital Imaging, Same-Day Crowns, Laser Dentistry</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S26" s="9" t="n">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Sachar Dental NYC</t>
+          <t>Midtown Dental Group Upper East Side</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>(212) 752-1163</t>
+          <t>(212) 588-1809</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>20 E 46th St Rm 1301, New York, NY 10017, USA</t>
+          <t>30 E 60th St Ste 2402, New York, NY 10022, USA</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
@@ -2956,25 +2956,25 @@
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>https://www.sachardental.com/</t>
+          <t>https://midtowndentalgroup.com/locations/uppereastside/</t>
         </is>
       </c>
       <c r="G27" s="12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>414</v>
+        <v>505</v>
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>Monday: 8:00 AM – 6:00 PM</t>
+          <t>Monday: 9:00 AM – 5:00 PM</t>
         </is>
       </c>
       <c r="J27" s="12" t="n">
-        <v>40.7554749</v>
+        <v>40.763742</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>-73.9779336</v>
+        <v>-73.97019589999999</v>
       </c>
       <c r="L27" s="13" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="M27" s="13" t="inlineStr">
         <is>
-          <t>1163 dentists</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N27" s="13" t="inlineStr">
@@ -2998,17 +2998,17 @@
       </c>
       <c r="P27" s="13" t="inlineStr">
         <is>
-          <t>Since 1998</t>
+          <t>Since 2018</t>
         </is>
       </c>
       <c r="Q27" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, LinkedIn</t>
+          <t>Facebook, Instagram</t>
         </is>
       </c>
       <c r="R27" s="13" t="inlineStr">
         <is>
-          <t>ZocDoc, Digital Imaging</t>
+          <t>ZocDoc</t>
         </is>
       </c>
       <c r="S27" s="12" t="n">
@@ -3026,17 +3026,17 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Midtown Dental Group Upper East Side</t>
+          <t>Midtown Dental Group Fashion District</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>(212) 588-1809</t>
+          <t>(212) 730-4440</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>30 E 60th St Ste 2402, New York, NY 10022, USA</t>
+          <t>241 W 37th St Ground Floor, New York, NY 10018, USA</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -3046,25 +3046,25 @@
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>https://midtowndentalgroup.com/locations/uppereastside/</t>
+          <t>http://www.midtowndentalgroup.com/</t>
         </is>
       </c>
       <c r="G28" s="9" t="n">
         <v>4.9</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>505</v>
+        <v>734</v>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 5:00 PM</t>
+          <t>Monday: 9:00 AM – 5:45 PM</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>40.763742</v>
+        <v>40.7538706</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>-73.97019589999999</v>
+        <v>-73.9909457</v>
       </c>
       <c r="L28" s="10" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="M28" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4 dentists</t>
         </is>
       </c>
       <c r="N28" s="10" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="P28" s="10" t="inlineStr">
         <is>
-          <t>Since 2018</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q28" s="10" t="inlineStr">
@@ -3116,17 +3116,17 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>My NYC Dentist - 34th Street Dental</t>
+          <t>Preferred Dental Care - Chelsea Dentist</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>(212) 564-8164</t>
+          <t>(212) 594-7171</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>225 W 35th St #2, New York, NY 10001, USA</t>
+          <t>135 W 27th St, New York, NY 10001, USA</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
@@ -3136,25 +3136,25 @@
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>http://www.mynyc-dentist.com/</t>
+          <t>https://www.preferreddentalcare.com/locations/chelsea-ny-location</t>
         </is>
       </c>
       <c r="G29" s="12" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>498</v>
+        <v>2341</v>
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>Monday: 8:30 AM – 6:00 PM</t>
+          <t>Monday: 7:00 AM – 9:00 PM</t>
         </is>
       </c>
       <c r="J29" s="12" t="n">
-        <v>40.7522776</v>
+        <v>40.7462879</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>-73.991056</v>
+        <v>-73.9924206</v>
       </c>
       <c r="L29" s="13" t="inlineStr">
         <is>
@@ -3168,27 +3168,27 @@
       </c>
       <c r="N29" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O29" s="13" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P29" s="13" t="inlineStr">
         <is>
-          <t>Since 2009</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q29" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram</t>
+          <t>Facebook, Instagram, Twitter/X, YouTube</t>
         </is>
       </c>
       <c r="R29" s="13" t="inlineStr">
         <is>
-          <t>ZocDoc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S29" s="12" t="n">
@@ -3206,17 +3206,17 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Group Health Dental</t>
+          <t>Dental House</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>(332) 249-1842</t>
+          <t>(212) 888-3384</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>230 W 41st St 15th Floor, New York, NY 10036, USA</t>
+          <t>41 7th Ave, New York, NY 10011, USA</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -3226,29 +3226,29 @@
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>https://grouphealthdental.com/</t>
+          <t>http://www.dentalhousenyc.com/</t>
         </is>
       </c>
       <c r="G30" s="9" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>1531</v>
+        <v>793</v>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 5:00 PM</t>
+          <t>Monday: 9:00 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>40.7557231</v>
+        <v>40.7379183</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>-73.9888607</v>
+        <v>-73.99990369999999</v>
       </c>
       <c r="L30" s="10" t="inlineStr">
         <is>
-          <t>General Dentistry, Cosmetic, Orthodontics, Periodontics</t>
+          <t>Cosmetic, Implants, Orthodontics, Endodontics</t>
         </is>
       </c>
       <c r="M30" s="10" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O30" s="10" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P30" s="10" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Manhattan Bridge Orthodontics</t>
+          <t>Modern Dental of Manhattan</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>(212) 274-0477</t>
+          <t>(212) 758-1000</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>77 Bowery 6th Floor, New York, NY 10002, USA</t>
+          <t>425 Madison Ave Rm 500, New York, NY 10017, USA</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
@@ -3316,44 +3316,44 @@
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>https://www.manhattanbridgeortho.com/</t>
+          <t>https://www.manhattandentists.com/</t>
         </is>
       </c>
       <c r="G31" s="12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>1514</v>
+        <v>235</v>
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>Monday: 10:00 AM – 7:00 PM</t>
+          <t>Monday: 9:00 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J31" s="12" t="n">
-        <v>40.71666949999999</v>
+        <v>40.7569869</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>-73.99553539999999</v>
+        <v>-73.975942</v>
       </c>
       <c r="L31" s="13" t="inlineStr">
         <is>
-          <t>Orthodontics</t>
+          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
         </is>
       </c>
       <c r="M31" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9497 dentists</t>
         </is>
       </c>
       <c r="N31" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O31" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="P31" s="13" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="Q31" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, YouTube</t>
+          <t>Facebook, Instagram</t>
         </is>
       </c>
       <c r="R31" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ZocDoc</t>
         </is>
       </c>
       <c r="S31" s="12" t="n">
@@ -3386,17 +3386,17 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>iSmile Orthodontics - NYC</t>
+          <t>Beautiful Smiles Dental Associates</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>(646) 863-2181</t>
+          <t>(516) 715-5650</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>4779 Broadway, New York, NY 10034, USA</t>
+          <t>2 W 46th St Ste 1003 10th Floor, New York, NY 10036, USA</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -3406,29 +3406,29 @@
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>https://ismileorthodontics.com/inwood/</t>
+          <t>https://www.beautifulsmilesdentalassociates.com/</t>
         </is>
       </c>
       <c r="G32" s="9" t="n">
         <v>4.9</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>1006</v>
+        <v>815</v>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 6:00 PM</t>
+          <t>Monday: 8:30 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>40.8659992</v>
+        <v>40.756096</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>-73.92655979999999</v>
+        <v>-73.9798129</v>
       </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
-          <t>Orthodontics</t>
+          <t>General Dentistry, Cosmetic, Orthodontics, Endodontics</t>
         </is>
       </c>
       <c r="M32" s="10" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="Q32" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, Twitter/X, LinkedIn, YouTube</t>
+          <t>Facebook, Instagram</t>
         </is>
       </c>
       <c r="R32" s="10" t="inlineStr">
         <is>
-          <t>Patient Portal</t>
+          <t>Digital Imaging</t>
         </is>
       </c>
       <c r="S32" s="9" t="n">
@@ -3476,17 +3476,17 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>NYC Orthodontics</t>
+          <t>The Exchange Dental Group</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>(212) 245-5121</t>
+          <t>(646) 780-5410</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>30 Central Park S RM 2A, New York, NY 10019, USA</t>
+          <t>39 Broadway Rm 2115, New York, NY 10006, USA</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
@@ -3496,29 +3496,29 @@
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>https://www.orthonyc.com/</t>
+          <t>https://www.theexchangedentalgroup.com/</t>
         </is>
       </c>
       <c r="G33" s="12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>54</v>
+        <v>1249</v>
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>Monday: 12:00 – 6:30 PM</t>
+          <t>Monday: 8:00 AM – 7:00 PM</t>
         </is>
       </c>
       <c r="J33" s="12" t="n">
-        <v>40.7649517</v>
+        <v>40.7063221</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>-73.9750827</v>
+        <v>-74.01333289999999</v>
       </c>
       <c r="L33" s="13" t="inlineStr">
         <is>
-          <t>Cosmetic, Orthodontics, Endodontics</t>
+          <t>General Dentistry, Cosmetic, Implants, Orthodontics</t>
         </is>
       </c>
       <c r="M33" s="13" t="inlineStr">
@@ -3538,17 +3538,17 @@
       </c>
       <c r="P33" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Since 1982</t>
         </is>
       </c>
       <c r="Q33" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Facebook, Instagram</t>
         </is>
       </c>
       <c r="R33" s="13" t="inlineStr">
         <is>
-          <t>ZocDoc, Digital Imaging</t>
+          <t>ZocDoc, Teledentistry, Digital Imaging, Laser Dentistry</t>
         </is>
       </c>
       <c r="S33" s="12" t="n">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Brite Orthodontics - Harlem (Central Park North Orthodontics)</t>
+          <t>Manhattan Bridge Orthodontics</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>(212) 866-9800</t>
+          <t>(212) 274-0477</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>1851 Adam Clayton Powell Jr Blvd, New York, NY 10026, USA</t>
+          <t>77 Bowery 6th Floor, New York, NY 10002, USA</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -3586,29 +3586,29 @@
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>https://www.briteorthodontics.com/locations/newyork-ny/</t>
+          <t>https://www.manhattanbridgeortho.com/</t>
         </is>
       </c>
       <c r="G34" s="9" t="n">
         <v>4.9</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>673</v>
+        <v>1514</v>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 5:00 PM</t>
+          <t>Monday: 10:00 AM – 7:00 PM</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>40.8009348</v>
+        <v>40.71666949999999</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>-73.95373900000001</v>
+        <v>-73.99553539999999</v>
       </c>
       <c r="L34" s="10" t="inlineStr">
         <is>
-          <t>General Dentistry, Orthodontics, Periodontics, Emergency</t>
+          <t>Orthodontics</t>
         </is>
       </c>
       <c r="M34" s="10" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="O34" s="10" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P34" s="10" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="Q34" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, LinkedIn</t>
+          <t>Facebook, Instagram, YouTube</t>
         </is>
       </c>
       <c r="R34" s="10" t="inlineStr">
@@ -3656,17 +3656,17 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Goodman Orthodontics</t>
+          <t>iSmile Orthodontics - NYC</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>(212) 688-4663</t>
+          <t>(646) 863-2181</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>440 E 57th St B, New York, NY 10022, USA</t>
+          <t>4779 Broadway, New York, NY 10034, USA</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
@@ -3676,25 +3676,25 @@
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>http://www.goodortho.com/</t>
+          <t>https://ismileorthodontics.com/inwood/</t>
         </is>
       </c>
       <c r="G35" s="12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>275</v>
+        <v>1006</v>
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>Monday: 8:00 AM – 4:00 PM</t>
+          <t>Monday: 9:00 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J35" s="12" t="n">
-        <v>40.7575229</v>
+        <v>40.8659992</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>-73.9616418</v>
+        <v>-73.92655979999999</v>
       </c>
       <c r="L35" s="13" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="O35" s="13" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P35" s="13" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="Q35" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, YouTube, TikTok</t>
+          <t>Facebook, Instagram, Twitter/X, LinkedIn, YouTube</t>
         </is>
       </c>
       <c r="R35" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Patient Portal</t>
         </is>
       </c>
       <c r="S35" s="12" t="n">
@@ -3746,17 +3746,17 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Gramercy Orthodontics</t>
+          <t>NYC Orthodontics</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>(212) 777-9177</t>
+          <t>(212) 245-5121</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>200 E 15th St STE PRB, New York, NY 10003, USA</t>
+          <t>30 Central Park S RM 2A, New York, NY 10019, USA</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -3766,29 +3766,29 @@
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>https://gramercyorthonyc.com/</t>
+          <t>https://www.orthonyc.com/</t>
         </is>
       </c>
       <c r="G36" s="9" t="n">
         <v>5</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>161</v>
+        <v>54</v>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>Monday: 10:00 AM – 7:00 PM</t>
+          <t>Monday: 12:00 – 6:30 PM</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>40.7337844</v>
+        <v>40.7649517</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>-73.98647919999999</v>
+        <v>-73.9750827</v>
       </c>
       <c r="L36" s="10" t="inlineStr">
         <is>
-          <t>Orthodontics</t>
+          <t>Cosmetic, Orthodontics, Endodontics</t>
         </is>
       </c>
       <c r="M36" s="10" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="N36" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O36" s="10" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="Q36" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R36" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ZocDoc, Digital Imaging</t>
         </is>
       </c>
       <c r="S36" s="9" t="n">
@@ -3836,17 +3836,17 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Bronsky Orthodontics</t>
+          <t>Manhattan EastSide Orthodontics</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>(212) 758-0040</t>
+          <t>(212) 289-8989</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>530 Park Ave APT 1G, New York, NY 10065, USA</t>
+          <t>207 E 94th St #501, New York, NY 10128, USA</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
@@ -3856,29 +3856,29 @@
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>http://www.bronskyorthodontics.com/?utm_source=GMBlisting&amp;utm_medium=organic</t>
+          <t>https://manhattaneastsideorthodontics.com/</t>
         </is>
       </c>
       <c r="G37" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>481</v>
+        <v>429</v>
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>Monday: 8:00 AM – 5:00 PM</t>
+          <t>Monday: 9:00 AM – 5:00 PM</t>
         </is>
       </c>
       <c r="J37" s="12" t="n">
-        <v>40.7641462</v>
+        <v>40.783778</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>-73.96946849999999</v>
+        <v>-73.949438</v>
       </c>
       <c r="L37" s="13" t="inlineStr">
         <is>
-          <t>Orthodontics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M37" s="13" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="Q37" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, YouTube</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R37" s="13" t="inlineStr">
@@ -3926,17 +3926,17 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Manhattan EastSide Orthodontics</t>
+          <t>Brite Orthodontics - Harlem (Central Park North Orthodontics)</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>(212) 289-8989</t>
+          <t>(212) 866-9800</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>207 E 94th St #501, New York, NY 10128, USA</t>
+          <t>1851 Adam Clayton Powell Jr Blvd, New York, NY 10026, USA</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -3946,14 +3946,14 @@
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>https://manhattaneastsideorthodontics.com/</t>
+          <t>https://www.briteorthodontics.com/locations/newyork-ny/</t>
         </is>
       </c>
       <c r="G38" s="9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>429</v>
+        <v>673</v>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
@@ -3961,14 +3961,14 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>40.783778</v>
+        <v>40.8009348</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>-73.949438</v>
+        <v>-73.95373900000001</v>
       </c>
       <c r="L38" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>General Dentistry, Orthodontics, Periodontics, Emergency</t>
         </is>
       </c>
       <c r="M38" s="10" t="inlineStr">
@@ -3978,12 +3978,12 @@
       </c>
       <c r="N38" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O38" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="P38" s="10" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="Q38" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Facebook, Instagram, LinkedIn</t>
         </is>
       </c>
       <c r="R38" s="10" t="inlineStr">
@@ -4016,17 +4016,17 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Smile Pop - Dr. Courtney Barry Orthodontist</t>
+          <t>Goodman Orthodontics</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>(646) 770-2091</t>
+          <t>(212) 688-4663</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>76 Madison Ave, New York, NY 10016, USA</t>
+          <t>440 E 57th St B, New York, NY 10022, USA</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
@@ -4036,29 +4036,29 @@
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>http://www.smilepop.com/</t>
+          <t>http://www.goodortho.com/</t>
         </is>
       </c>
       <c r="G39" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>444</v>
+        <v>275</v>
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>Monday: 10:00 AM – 4:00 PM</t>
+          <t>Monday: 8:00 AM – 4:00 PM</t>
         </is>
       </c>
       <c r="J39" s="12" t="n">
-        <v>40.74397099999999</v>
+        <v>40.7575229</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>-73.9860561</v>
+        <v>-73.9616418</v>
       </c>
       <c r="L39" s="13" t="inlineStr">
         <is>
-          <t>Cosmetic, Orthodontics</t>
+          <t>Orthodontics</t>
         </is>
       </c>
       <c r="M39" s="13" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="N39" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O39" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="P39" s="13" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="Q39" s="13" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Facebook, Instagram, YouTube, TikTok</t>
         </is>
       </c>
       <c r="R39" s="13" t="inlineStr">
@@ -4106,17 +4106,17 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Salzer Orthodontics, Dr. Jennifer Salzer</t>
+          <t>Gramercy Orthodontics</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>(212) 755-2333</t>
+          <t>(212) 777-9177</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>553 Park Ave, New York, NY 10065, USA</t>
+          <t>200 E 15th St STE PRB, New York, NY 10003, USA</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -4126,25 +4126,25 @@
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>https://lsortho.com/contact-orthodontist-nyc</t>
+          <t>https://gramercyorthonyc.com/</t>
         </is>
       </c>
       <c r="G40" s="9" t="n">
         <v>5</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 6:00 PM</t>
+          <t>Monday: 10:00 AM – 7:00 PM</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>40.7645406</v>
+        <v>40.7337844</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>-73.9683215</v>
+        <v>-73.98647919999999</v>
       </c>
       <c r="L40" s="10" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="O40" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="P40" s="10" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="Q40" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, LinkedIn, YouTube, TikTok</t>
+          <t>Facebook, Instagram</t>
         </is>
       </c>
       <c r="R40" s="10" t="inlineStr">
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="S40" s="9" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="T40" s="11" t="inlineStr">
         <is>
@@ -4196,49 +4196,49 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Jackson Heights Orthodontics</t>
+          <t>Bronsky Orthodontics</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>(718) 335-4444</t>
+          <t>(212) 758-0040</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>37-43 77th St, Jackson Heights, NY 11372, USA</t>
+          <t>530 Park Ave APT 1G, New York, NY 10065, USA</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Jackson Heights</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>http://jhoortho.com/</t>
+          <t>http://www.bronskyorthodontics.com/?utm_source=GMBlisting&amp;utm_medium=organic</t>
         </is>
       </c>
       <c r="G41" s="12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>1337</v>
+        <v>481</v>
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 5:00 PM</t>
+          <t>Monday: 8:00 AM – 5:00 PM</t>
         </is>
       </c>
       <c r="J41" s="12" t="n">
-        <v>40.7479692</v>
+        <v>40.7641462</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>-73.88860989999999</v>
+        <v>-73.96946849999999</v>
       </c>
       <c r="L41" s="13" t="inlineStr">
         <is>
-          <t>Cosmetic, Orthodontics</t>
+          <t>Orthodontics</t>
         </is>
       </c>
       <c r="M41" s="13" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="N41" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O41" s="13" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="Q41" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram</t>
+          <t>Facebook, Instagram, YouTube</t>
         </is>
       </c>
       <c r="R41" s="13" t="inlineStr">
         <is>
-          <t>Teledentistry</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S41" s="12" t="n">
@@ -4286,17 +4286,17 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Wall Street Orthodontics</t>
+          <t>Smile Pop - Dr. Courtney Barry Orthodontist</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>(212) 871-9835</t>
+          <t>(646) 770-2091</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>111 Broadway APT 1707, New York, NY 10006, USA</t>
+          <t>76 Madison Ave, New York, NY 10016, USA</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -4306,29 +4306,29 @@
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>http://wallstreetortho.com/</t>
+          <t>http://www.smilepop.com/</t>
         </is>
       </c>
       <c r="G42" s="9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>87</v>
+        <v>444</v>
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 5:00 PM</t>
+          <t>Monday: 10:00 AM – 4:00 PM</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>40.7086853</v>
+        <v>40.74397099999999</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>-74.01154869999999</v>
+        <v>-73.9860561</v>
       </c>
       <c r="L42" s="10" t="inlineStr">
         <is>
-          <t>Orthodontics</t>
+          <t>Cosmetic, Orthodontics</t>
         </is>
       </c>
       <c r="M42" s="10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="N42" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O42" s="10" t="inlineStr">
@@ -4353,16 +4353,16 @@
       </c>
       <c r="Q42" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, YouTube</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="R42" s="10" t="inlineStr">
         <is>
-          <t>Teledentistry, Digital Imaging</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S42" s="9" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="T42" s="11" t="inlineStr">
         <is>
@@ -4376,17 +4376,17 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Fellow Orthodontist</t>
+          <t>Salzer Orthodontics, Dr. Jennifer Salzer</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>(917) 451-2999</t>
+          <t>(212) 755-2333</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>49 E 18th St, New York, NY 10003, USA</t>
+          <t>553 Park Ave, New York, NY 10065, USA</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
@@ -4396,29 +4396,29 @@
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>https://felloworthodontist.com/</t>
+          <t>https://lsortho.com/contact-orthodontist-nyc</t>
         </is>
       </c>
       <c r="G43" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>234</v>
+        <v>177</v>
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>Monday: 10:00 AM – 5:00 PM</t>
+          <t>Monday: 9:00 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J43" s="12" t="n">
-        <v>40.7375877</v>
+        <v>40.7645406</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>-73.98918399999999</v>
+        <v>-73.9683215</v>
       </c>
       <c r="L43" s="13" t="inlineStr">
         <is>
-          <t>Cosmetic, Orthodontics</t>
+          <t>Orthodontics</t>
         </is>
       </c>
       <c r="M43" s="13" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="N43" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O43" s="13" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P43" s="13" t="inlineStr">
@@ -4443,16 +4443,16 @@
       </c>
       <c r="Q43" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, Twitter/X</t>
+          <t>Facebook, Instagram, LinkedIn, YouTube, TikTok</t>
         </is>
       </c>
       <c r="R43" s="13" t="inlineStr">
         <is>
-          <t>Teledentistry</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S43" s="12" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="T43" s="11" t="inlineStr">
         <is>
@@ -4466,45 +4466,45 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Straight Set Orthodontics | Harlem</t>
+          <t>Jackson Heights Orthodontics</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>(212) 996-7300</t>
+          <t>(718) 335-4444</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>241 Malcolm X Blvd, New York, NY 10027, USA</t>
+          <t>37-43 77th St, Jackson Heights, NY 11372, USA</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Jackson Heights</t>
         </is>
       </c>
       <c r="F44" s="9" t="inlineStr">
         <is>
-          <t>https://www.straightsetortho.com/harlem</t>
+          <t>http://jhoortho.com/</t>
         </is>
       </c>
       <c r="G44" s="9" t="n">
         <v>4.8</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>677</v>
+        <v>1337</v>
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 6:00 PM</t>
+          <t>Monday: 9:00 AM – 5:00 PM</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>40.8060963</v>
+        <v>40.7479692</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>-73.94716439999999</v>
+        <v>-73.88860989999999</v>
       </c>
       <c r="L44" s="10" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
       </c>
       <c r="O44" s="10" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P44" s="10" t="inlineStr">
@@ -4556,17 +4556,17 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Central Park Orthodontics</t>
+          <t>Wall Street Orthodontics</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>(212) 362-4400</t>
+          <t>(212) 871-9835</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>271A Central Park West, (entrance on, W 87th St, New York, NY 10024, USA</t>
+          <t>111 Broadway APT 1707, New York, NY 10006, USA</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
@@ -4576,25 +4576,25 @@
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>https://www.centralparkorthodontics.com/</t>
+          <t>http://wallstreetortho.com/</t>
         </is>
       </c>
       <c r="G45" s="12" t="n">
         <v>4.9</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 6:00 PM</t>
+          <t>Monday: 9:00 AM – 5:00 PM</t>
         </is>
       </c>
       <c r="J45" s="12" t="n">
-        <v>40.786237</v>
+        <v>40.7086853</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>-73.969014</v>
+        <v>-74.01154869999999</v>
       </c>
       <c r="L45" s="13" t="inlineStr">
         <is>
@@ -4613,26 +4613,26 @@
       </c>
       <c r="O45" s="13" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P45" s="13" t="inlineStr">
         <is>
-          <t>Since 2006</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q45" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram</t>
+          <t>Facebook, Instagram, YouTube</t>
         </is>
       </c>
       <c r="R45" s="13" t="inlineStr">
         <is>
-          <t>ZocDoc</t>
+          <t>Teledentistry, Digital Imaging</t>
         </is>
       </c>
       <c r="S45" s="12" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="T45" s="11" t="inlineStr">
         <is>
@@ -4646,17 +4646,17 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Gibbs Orthodontic Associates, P.C : Invisalign, Braces and Dentofacial Orthopedics</t>
+          <t>Straight Set Orthodontics | Harlem</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>(212) 535-4111</t>
+          <t>(212) 996-7300</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>40 E 84th St, New York, NY 10028, USA</t>
+          <t>241 Malcolm X Blvd, New York, NY 10027, USA</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
@@ -4666,29 +4666,29 @@
       </c>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>https://www.gibbsortho.com/</t>
+          <t>https://www.straightsetortho.com/harlem</t>
         </is>
       </c>
       <c r="G46" s="9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>186</v>
+        <v>677</v>
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 5:00 PM</t>
+          <t>Monday: 9:00 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>40.7793093</v>
+        <v>40.8060963</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>-73.95947029999999</v>
+        <v>-73.94716439999999</v>
       </c>
       <c r="L46" s="10" t="inlineStr">
         <is>
-          <t>General Dentistry, Cosmetic, Orthodontics</t>
+          <t>Cosmetic, Orthodontics</t>
         </is>
       </c>
       <c r="M46" s="10" t="inlineStr">
@@ -4703,22 +4703,22 @@
       </c>
       <c r="O46" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="P46" s="10" t="inlineStr">
         <is>
-          <t>Since 1985</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q46" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, Twitter/X, LinkedIn, YouTube, TikTok</t>
+          <t>Facebook, Instagram</t>
         </is>
       </c>
       <c r="R46" s="10" t="inlineStr">
         <is>
-          <t>Teledentistry, Digital Imaging</t>
+          <t>Teledentistry</t>
         </is>
       </c>
       <c r="S46" s="9" t="n">
@@ -4736,17 +4736,17 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Orthodontics Center of NYC</t>
+          <t>Fellow Orthodontist</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>(646) 491-7133</t>
+          <t>(917) 451-2999</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>263 West End Ave Fl 1, New York, NY 10023, USA</t>
+          <t>49 E 18th St, New York, NY 10003, USA</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
@@ -4756,29 +4756,29 @@
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>https://www.orthodonticscenternyc.com/</t>
+          <t>https://felloworthodontist.com/</t>
         </is>
       </c>
       <c r="G47" s="12" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>12</v>
+        <v>234</v>
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 6:00 PM</t>
+          <t>Monday: 10:00 AM – 5:00 PM</t>
         </is>
       </c>
       <c r="J47" s="12" t="n">
-        <v>40.7800807</v>
+        <v>40.7375877</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>-73.9845136</v>
+        <v>-73.98918399999999</v>
       </c>
       <c r="L47" s="13" t="inlineStr">
         <is>
-          <t>Orthodontics</t>
+          <t>Cosmetic, Orthodontics</t>
         </is>
       </c>
       <c r="M47" s="13" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="N47" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O47" s="13" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="Q47" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, Twitter/X, LinkedIn</t>
+          <t>Facebook, Instagram, Twitter/X</t>
         </is>
       </c>
       <c r="R47" s="13" t="inlineStr">
@@ -4812,11 +4812,11 @@
         </is>
       </c>
       <c r="S47" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="T47" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
+        <v>100</v>
+      </c>
+      <c r="T47" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -4826,17 +4826,17 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Lemchen Salzer Orthodontics</t>
+          <t>Central Park Orthodontics</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>(212) 755-2333</t>
+          <t>(212) 362-4400</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>553 Park Ave, New York, NY 10065, USA</t>
+          <t>271A Central Park West, (entrance on, W 87th St, New York, NY 10024, USA</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -4846,14 +4846,14 @@
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>http://www.lsortho.com/</t>
+          <t>https://www.centralparkorthodontics.com/</t>
         </is>
       </c>
       <c r="G48" s="9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>313</v>
+        <v>60</v>
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>40.76448</v>
+        <v>40.786237</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>-73.96826279999999</v>
+        <v>-73.969014</v>
       </c>
       <c r="L48" s="10" t="inlineStr">
         <is>
@@ -4883,26 +4883,26 @@
       </c>
       <c r="O48" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="P48" s="10" t="inlineStr">
         <is>
-          <t>Since 1974</t>
+          <t>Since 2006</t>
         </is>
       </c>
       <c r="Q48" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, LinkedIn, YouTube, TikTok</t>
+          <t>Facebook, Instagram</t>
         </is>
       </c>
       <c r="R48" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ZocDoc</t>
         </is>
       </c>
       <c r="S48" s="9" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="T48" s="11" t="inlineStr">
         <is>
@@ -4916,17 +4916,17 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Manhattan Family Orthodontics-Uptown</t>
+          <t>Gibbs Orthodontic Associates, P.C : Invisalign, Braces and Dentofacial Orthopedics</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>(347) 767-5668</t>
+          <t>(212) 535-4111</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>207 E 63rd St, New York, NY 10022, USA</t>
+          <t>40 E 84th St, New York, NY 10028, USA</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
@@ -4936,29 +4936,29 @@
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>https://www.manhattanfamilyorthodontics.com/</t>
+          <t>https://www.gibbsortho.com/</t>
         </is>
       </c>
       <c r="G49" s="12" t="n">
         <v>4.9</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>Monday: 1:00 – 6:00 PM</t>
+          <t>Monday: 9:00 AM – 5:00 PM</t>
         </is>
       </c>
       <c r="J49" s="12" t="n">
-        <v>40.7640232</v>
+        <v>40.7793093</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>-73.96417579999999</v>
+        <v>-73.95947029999999</v>
       </c>
       <c r="L49" s="13" t="inlineStr">
         <is>
-          <t>General Dentistry, Orthodontics</t>
+          <t>General Dentistry, Cosmetic, Orthodontics</t>
         </is>
       </c>
       <c r="M49" s="13" t="inlineStr">
@@ -4968,27 +4968,27 @@
       </c>
       <c r="N49" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O49" s="13" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P49" s="13" t="inlineStr">
         <is>
-          <t>Since 2019</t>
+          <t>Since 1985</t>
         </is>
       </c>
       <c r="Q49" s="13" t="inlineStr">
         <is>
-          <t>Facebook, Instagram</t>
+          <t>Facebook, Instagram, Twitter/X, LinkedIn, YouTube, TikTok</t>
         </is>
       </c>
       <c r="R49" s="13" t="inlineStr">
         <is>
-          <t>ZocDoc, Teledentistry</t>
+          <t>Teledentistry, Digital Imaging</t>
         </is>
       </c>
       <c r="S49" s="12" t="n">
@@ -5006,17 +5006,17 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>Mid-Manhattan Oral Surgery, PC</t>
+          <t>Orthodontics Center of NYC</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>(212) 918-1859</t>
+          <t>(646) 491-7133</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>36 West 44th Street, Suite 600 Between, 5th and 6th Avenue, New York, NY 10036, USA</t>
+          <t>263 West End Ave Fl 1, New York, NY 10023, USA</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
@@ -5026,29 +5026,29 @@
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>https://www.midmanhattanoralsurgery.com/</t>
+          <t>https://www.orthodonticscenternyc.com/</t>
         </is>
       </c>
       <c r="G50" s="9" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>895</v>
+        <v>12</v>
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
-          <t>Monday: 8:00 AM – 5:00 PM</t>
+          <t>Monday: 9:00 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>40.7555517</v>
+        <v>40.7800807</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>-73.9819631</v>
+        <v>-73.9845136</v>
       </c>
       <c r="L50" s="10" t="inlineStr">
         <is>
-          <t>Implants, Oral Surgery</t>
+          <t>Orthodontics</t>
         </is>
       </c>
       <c r="M50" s="10" t="inlineStr">
@@ -5058,12 +5058,12 @@
       </c>
       <c r="N50" s="10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O50" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="P50" s="10" t="inlineStr">
@@ -5073,20 +5073,20 @@
       </c>
       <c r="Q50" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Facebook, Instagram, Twitter/X, LinkedIn</t>
         </is>
       </c>
       <c r="R50" s="10" t="inlineStr">
         <is>
-          <t>Digital Imaging</t>
+          <t>Teledentistry</t>
         </is>
       </c>
       <c r="S50" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="T50" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
+        <v>68</v>
+      </c>
+      <c r="T50" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -5096,17 +5096,17 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>New York Oral &amp; Maxillofacial Surgery &amp; Dental Implant Center</t>
+          <t>Lemchen Salzer Orthodontics</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>(646) 681-7068</t>
+          <t>(212) 755-2333</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>800B 5th Ave Ste 1, New York, NY 10065, USA</t>
+          <t>553 Park Ave, New York, NY 10065, USA</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
@@ -5116,29 +5116,29 @@
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>https://www.new-york-oral-surgery.com/</t>
+          <t>http://www.lsortho.com/</t>
         </is>
       </c>
       <c r="G51" s="12" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>12</v>
+        <v>313</v>
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 5:00 PM</t>
+          <t>Monday: 9:00 AM – 6:00 PM</t>
         </is>
       </c>
       <c r="J51" s="12" t="n">
-        <v>40.7655359</v>
+        <v>40.76448</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>-73.97173069999999</v>
+        <v>-73.96826279999999</v>
       </c>
       <c r="L51" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Orthodontics</t>
         </is>
       </c>
       <c r="M51" s="13" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="P51" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Since 1974</t>
         </is>
       </c>
       <c r="Q51" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Facebook, Instagram, LinkedIn, YouTube, TikTok</t>
         </is>
       </c>
       <c r="R51" s="13" t="inlineStr">
@@ -5172,11 +5172,11 @@
         </is>
       </c>
       <c r="S51" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="T51" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
+        <v>100</v>
+      </c>
+      <c r="T51" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5186,49 +5186,49 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Oral Surgery of Northern New York</t>
+          <t>Manhattan Family Orthodontics-Uptown</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>(315) 786-3990</t>
+          <t>(347) 767-5668</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>163 S Bellew Ave, Watertown, NY 13601, USA</t>
+          <t>207 E 63rd St, New York, NY 10022, USA</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Watertown</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>https://www.oralsurgerynny.com/</t>
+          <t>https://www.manhattanfamilyorthodontics.com/</t>
         </is>
       </c>
       <c r="G52" s="9" t="n">
         <v>4.9</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>994</v>
+        <v>159</v>
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
-          <t>Monday: 7:30 AM – 4:30 PM</t>
+          <t>Monday: 1:00 – 6:00 PM</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>43.9743256</v>
+        <v>40.7640232</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>-75.9319438</v>
+        <v>-73.96417579999999</v>
       </c>
       <c r="L52" s="10" t="inlineStr">
         <is>
-          <t>Implants, Oral Surgery</t>
+          <t>General Dentistry, Orthodontics</t>
         </is>
       </c>
       <c r="M52" s="10" t="inlineStr">
@@ -5248,17 +5248,17 @@
       </c>
       <c r="P52" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Since 2019</t>
         </is>
       </c>
       <c r="Q52" s="10" t="inlineStr">
         <is>
-          <t>Facebook, Instagram, Twitter/X</t>
+          <t>Facebook, Instagram</t>
         </is>
       </c>
       <c r="R52" s="10" t="inlineStr">
         <is>
-          <t>Digital Imaging</t>
+          <t>ZocDoc, Teledentistry</t>
         </is>
       </c>
       <c r="S52" s="9" t="n">
@@ -5276,17 +5276,17 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>David A. Koslovsky, DDS, FACS, FACD</t>
+          <t>Mid-Manhattan Oral Surgery, PC</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>(212) 888-4760</t>
+          <t>(212) 918-1859</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>800B 5th Ave Ste 1, New York, NY 10065, USA</t>
+          <t>36 West 44th Street, Suite 600 Between, 5th and 6th Avenue, New York, NY 10036, USA</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
@@ -5296,29 +5296,29 @@
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>https://www.new-york-oral-surgery.com/oral-surgeon-ny/oral-surgeon-new-york-city.htm</t>
+          <t>https://www.midmanhattanoralsurgery.com/</t>
         </is>
       </c>
       <c r="G53" s="12" t="n">
         <v>4.9</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>146</v>
+        <v>895</v>
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>Monday: 9:00 AM – 5:00 PM</t>
+          <t>Monday: 8:00 AM – 5:00 PM</t>
         </is>
       </c>
       <c r="J53" s="12" t="n">
-        <v>40.7655359</v>
+        <v>40.7555517</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>-73.97173069999999</v>
+        <v>-73.9819631</v>
       </c>
       <c r="L53" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Implants, Oral Surgery</t>
         </is>
       </c>
       <c r="M53" s="13" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="N53" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O53" s="13" t="inlineStr">
@@ -5348,11 +5348,11 @@
       </c>
       <c r="R53" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Digital Imaging</t>
         </is>
       </c>
       <c r="S53" s="12" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="T53" s="11" t="inlineStr">
         <is>
